--- a/ind_1/Количество построенных квартир.xlsx
+++ b/ind_1/Количество построенных квартир.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t>Алтайский край</t>
   </si>
@@ -179,9 +179,6 @@
   </si>
   <si>
     <t>Сахалинская область</t>
-  </si>
-  <si>
-    <t>Российская Федерация</t>
   </si>
   <si>
     <t>Свердловская область</t>
@@ -306,7 +303,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -553,7 +549,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="95" width="8.71"/>
+    <col customWidth="1" min="1" max="93" width="8.71"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -654,190 +650,184 @@
         <v>31</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="BO2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="BS2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="BT2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BU2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="BW2" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BY2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BZ2" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="CA2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="CB2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="CC2" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="CD2" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="CE2" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="CF2" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="CG2" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="CH2" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="CI2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="CJ2" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="CK2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="CL2" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="CM2" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="CN2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="CO2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="CP2" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="CQ2" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="4">
@@ -941,189 +931,183 @@
         <v>8099.0</v>
       </c>
       <c r="AH4" s="1">
+        <v>935.0</v>
+      </c>
+      <c r="AI4" s="1">
         <v>0.0</v>
       </c>
-      <c r="AI4" s="1">
-        <v>935.0</v>
-      </c>
-      <c r="AJ4" s="1">
+      <c r="AJ4" s="2">
+        <v>2199.0</v>
+      </c>
+      <c r="AK4" s="2">
+        <v>6292.0</v>
+      </c>
+      <c r="AL4" s="2">
+        <v>15191.0</v>
+      </c>
+      <c r="AM4" s="2">
+        <v>5410.0</v>
+      </c>
+      <c r="AN4" s="2">
+        <v>4136.0</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>99.0</v>
+      </c>
+      <c r="AP4" s="2">
+        <v>49233.0</v>
+      </c>
+      <c r="AQ4" s="2">
+        <v>24889.0</v>
+      </c>
+      <c r="AR4" s="1">
+        <v>467.0</v>
+      </c>
+      <c r="AS4" s="2">
+        <v>1310.0</v>
+      </c>
+      <c r="AT4" s="2">
+        <v>2596.0</v>
+      </c>
+      <c r="AU4" s="2">
+        <v>6940.0</v>
+      </c>
+      <c r="AV4" s="2">
+        <v>3152.0</v>
+      </c>
+      <c r="AW4" s="2">
+        <v>3722.0</v>
+      </c>
+      <c r="AX4" s="2">
+        <v>2868.0</v>
+      </c>
+      <c r="AY4" s="2">
+        <v>2903.0</v>
+      </c>
+      <c r="AZ4" s="2">
+        <v>4546.0</v>
+      </c>
+      <c r="BA4" s="2">
+        <v>1190.0</v>
+      </c>
+      <c r="BB4" s="2">
+        <v>11241.0</v>
+      </c>
+      <c r="BC4" s="2">
+        <v>3230.0</v>
+      </c>
+      <c r="BD4" s="2">
+        <v>5007.0</v>
+      </c>
+      <c r="BE4" s="1">
+        <v>890.0</v>
+      </c>
+      <c r="BF4" s="2">
+        <v>7824.0</v>
+      </c>
+      <c r="BG4" s="2">
+        <v>2170.0</v>
+      </c>
+      <c r="BH4" s="2">
+        <v>2846.0</v>
+      </c>
+      <c r="BI4" s="2">
+        <v>2609.0</v>
+      </c>
+      <c r="BJ4" s="2">
+        <v>6471.0</v>
+      </c>
+      <c r="BK4" s="2">
+        <v>3034.0</v>
+      </c>
+      <c r="BL4" s="2">
+        <v>13085.0</v>
+      </c>
+      <c r="BM4" s="2">
+        <v>5486.0</v>
+      </c>
+      <c r="BN4" s="2">
+        <v>1449.0</v>
+      </c>
+      <c r="BO4" s="2">
+        <v>2591.0</v>
+      </c>
+      <c r="BP4" s="2">
+        <v>8870.0</v>
+      </c>
+      <c r="BQ4" s="1">
+        <v>902.0</v>
+      </c>
+      <c r="BR4" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="BS4" s="2">
+        <v>1855.0</v>
+      </c>
+      <c r="BT4" s="1">
+        <v>650.0</v>
+      </c>
+      <c r="BU4" s="2">
+        <v>2317.0</v>
+      </c>
+      <c r="BV4" s="2">
+        <v>15349.0</v>
+      </c>
+      <c r="BW4" s="2">
+        <v>2086.0</v>
+      </c>
+      <c r="BX4" s="2">
+        <v>3904.0</v>
+      </c>
+      <c r="BY4" s="2">
+        <v>1562.0</v>
+      </c>
+      <c r="BZ4" s="1">
+        <v>400.0</v>
+      </c>
+      <c r="CA4" s="1">
+        <v>441.0</v>
+      </c>
+      <c r="CB4" s="1">
+        <v>834.0</v>
+      </c>
+      <c r="CC4" s="2">
+        <v>3879.0</v>
+      </c>
+      <c r="CD4" s="2">
+        <v>1636.0</v>
+      </c>
+      <c r="CE4" s="2">
+        <v>2128.0</v>
+      </c>
+      <c r="CF4" s="2">
+        <v>1402.0</v>
+      </c>
+      <c r="CG4" s="1">
+        <v>391.0</v>
+      </c>
+      <c r="CH4" s="2">
+        <v>19411.0</v>
+      </c>
+      <c r="CI4" s="1">
+        <v>595.0</v>
+      </c>
+      <c r="CJ4" s="2">
+        <v>3328.0</v>
+      </c>
+      <c r="CK4" s="2">
+        <v>1511.0</v>
+      </c>
+      <c r="CL4" s="1">
         <v>0.0</v>
       </c>
-      <c r="AK4" s="2">
-        <v>2199.0</v>
-      </c>
-      <c r="AL4" s="2">
-        <v>6292.0</v>
-      </c>
-      <c r="AM4" s="2">
-        <v>15191.0</v>
-      </c>
-      <c r="AN4" s="2">
-        <v>5410.0</v>
-      </c>
-      <c r="AO4" s="2">
-        <v>4136.0</v>
-      </c>
-      <c r="AP4" s="1">
-        <v>99.0</v>
-      </c>
-      <c r="AQ4" s="2">
-        <v>49233.0</v>
-      </c>
-      <c r="AR4" s="2">
-        <v>24889.0</v>
-      </c>
-      <c r="AS4" s="1">
-        <v>467.0</v>
-      </c>
-      <c r="AT4" s="2">
-        <v>1310.0</v>
-      </c>
-      <c r="AU4" s="2">
-        <v>2596.0</v>
-      </c>
-      <c r="AV4" s="2">
-        <v>6940.0</v>
-      </c>
-      <c r="AW4" s="2">
-        <v>3152.0</v>
-      </c>
-      <c r="AX4" s="2">
-        <v>3722.0</v>
-      </c>
-      <c r="AY4" s="2">
-        <v>2868.0</v>
-      </c>
-      <c r="AZ4" s="2">
-        <v>2903.0</v>
-      </c>
-      <c r="BA4" s="2">
-        <v>4546.0</v>
-      </c>
-      <c r="BB4" s="2">
-        <v>1190.0</v>
-      </c>
-      <c r="BC4" s="2">
-        <v>11241.0</v>
-      </c>
-      <c r="BD4" s="2">
-        <v>3230.0</v>
-      </c>
-      <c r="BE4" s="2">
-        <v>5007.0</v>
-      </c>
-      <c r="BF4" s="1">
-        <v>890.0</v>
-      </c>
-      <c r="BG4" s="1">
-        <v>373.0</v>
-      </c>
-      <c r="BH4" s="2">
-        <v>7824.0</v>
-      </c>
-      <c r="BI4" s="2">
-        <v>2170.0</v>
-      </c>
-      <c r="BJ4" s="2">
-        <v>2846.0</v>
-      </c>
-      <c r="BK4" s="2">
-        <v>2609.0</v>
-      </c>
-      <c r="BL4" s="2">
-        <v>6471.0</v>
-      </c>
-      <c r="BM4" s="2">
-        <v>3034.0</v>
-      </c>
-      <c r="BN4" s="2">
-        <v>13085.0</v>
-      </c>
-      <c r="BO4" s="2">
-        <v>5486.0</v>
-      </c>
-      <c r="BP4" s="2">
-        <v>1449.0</v>
-      </c>
-      <c r="BQ4" s="2">
-        <v>2591.0</v>
-      </c>
-      <c r="BR4" s="2">
-        <v>8870.0</v>
-      </c>
-      <c r="BS4" s="1">
-        <v>902.0</v>
-      </c>
-      <c r="BT4" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="BU4" s="2">
-        <v>1855.0</v>
-      </c>
-      <c r="BV4" s="1">
-        <v>650.0</v>
-      </c>
-      <c r="BW4" s="2">
-        <v>2317.0</v>
-      </c>
-      <c r="BX4" s="2">
-        <v>15349.0</v>
-      </c>
-      <c r="BY4" s="2">
-        <v>2086.0</v>
-      </c>
-      <c r="BZ4" s="2">
-        <v>3904.0</v>
-      </c>
-      <c r="CA4" s="2">
-        <v>1562.0</v>
-      </c>
-      <c r="CB4" s="1">
-        <v>400.0</v>
-      </c>
-      <c r="CC4" s="1">
-        <v>441.0</v>
-      </c>
-      <c r="CD4" s="1">
-        <v>834.0</v>
-      </c>
-      <c r="CE4" s="2">
-        <v>3879.0</v>
-      </c>
-      <c r="CF4" s="2">
-        <v>1636.0</v>
-      </c>
-      <c r="CG4" s="2">
-        <v>2128.0</v>
-      </c>
-      <c r="CH4" s="2">
-        <v>1402.0</v>
-      </c>
-      <c r="CI4" s="1">
-        <v>391.0</v>
-      </c>
-      <c r="CJ4" s="2">
-        <v>19411.0</v>
-      </c>
-      <c r="CK4" s="1">
-        <v>595.0</v>
-      </c>
-      <c r="CL4" s="2">
-        <v>3328.0</v>
-      </c>
       <c r="CM4" s="2">
-        <v>1511.0</v>
-      </c>
-      <c r="CN4" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="CO4" s="2">
         <v>5308.0</v>
       </c>
-      <c r="CP4" s="2">
+      <c r="CN4" s="2">
         <v>3409.0</v>
       </c>
-      <c r="CQ4" s="1">
+      <c r="CO4" s="1">
         <v>144.0</v>
       </c>
     </row>
@@ -1227,190 +1211,184 @@
       <c r="AG5" s="2">
         <v>8556.0</v>
       </c>
-      <c r="AH5" s="1">
+      <c r="AH5" s="2">
+        <v>1233.0</v>
+      </c>
+      <c r="AI5" s="1">
         <v>0.0</v>
       </c>
-      <c r="AI5" s="2">
-        <v>1233.0</v>
-      </c>
-      <c r="AJ5" s="1">
+      <c r="AJ5" s="2">
+        <v>2266.0</v>
+      </c>
+      <c r="AK5" s="2">
+        <v>5032.0</v>
+      </c>
+      <c r="AL5" s="2">
+        <v>15179.0</v>
+      </c>
+      <c r="AM5" s="2">
+        <v>5198.0</v>
+      </c>
+      <c r="AN5" s="2">
+        <v>4378.0</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>105.0</v>
+      </c>
+      <c r="AP5" s="2">
+        <v>52204.0</v>
+      </c>
+      <c r="AQ5" s="2">
+        <v>29163.0</v>
+      </c>
+      <c r="AR5" s="1">
+        <v>107.0</v>
+      </c>
+      <c r="AS5" s="2">
+        <v>1336.0</v>
+      </c>
+      <c r="AT5" s="2">
+        <v>2933.0</v>
+      </c>
+      <c r="AU5" s="2">
+        <v>5292.0</v>
+      </c>
+      <c r="AV5" s="2">
+        <v>2112.0</v>
+      </c>
+      <c r="AW5" s="2">
+        <v>4614.0</v>
+      </c>
+      <c r="AX5" s="2">
+        <v>2722.0</v>
+      </c>
+      <c r="AY5" s="2">
+        <v>2362.0</v>
+      </c>
+      <c r="AZ5" s="2">
+        <v>6785.0</v>
+      </c>
+      <c r="BA5" s="2">
+        <v>1312.0</v>
+      </c>
+      <c r="BB5" s="2">
+        <v>10869.0</v>
+      </c>
+      <c r="BC5" s="2">
+        <v>1907.0</v>
+      </c>
+      <c r="BD5" s="2">
+        <v>5893.0</v>
+      </c>
+      <c r="BE5" s="1">
+        <v>396.0</v>
+      </c>
+      <c r="BF5" s="2">
+        <v>7535.0</v>
+      </c>
+      <c r="BG5" s="2">
+        <v>2049.0</v>
+      </c>
+      <c r="BH5" s="2">
+        <v>2341.0</v>
+      </c>
+      <c r="BI5" s="2">
+        <v>2911.0</v>
+      </c>
+      <c r="BJ5" s="2">
+        <v>5338.0</v>
+      </c>
+      <c r="BK5" s="2">
+        <v>1451.0</v>
+      </c>
+      <c r="BL5" s="2">
+        <v>18116.0</v>
+      </c>
+      <c r="BM5" s="2">
+        <v>11049.0</v>
+      </c>
+      <c r="BN5" s="2">
+        <v>1617.0</v>
+      </c>
+      <c r="BO5" s="2">
+        <v>2961.0</v>
+      </c>
+      <c r="BP5" s="2">
+        <v>7963.0</v>
+      </c>
+      <c r="BQ5" s="2">
+        <v>1119.0</v>
+      </c>
+      <c r="BR5" s="1">
+        <v>172.0</v>
+      </c>
+      <c r="BS5" s="2">
+        <v>2364.0</v>
+      </c>
+      <c r="BT5" s="1">
+        <v>843.0</v>
+      </c>
+      <c r="BU5" s="2">
+        <v>2182.0</v>
+      </c>
+      <c r="BV5" s="2">
+        <v>17117.0</v>
+      </c>
+      <c r="BW5" s="2">
+        <v>2396.0</v>
+      </c>
+      <c r="BX5" s="2">
+        <v>5318.0</v>
+      </c>
+      <c r="BY5" s="2">
+        <v>1791.0</v>
+      </c>
+      <c r="BZ5" s="1">
+        <v>245.0</v>
+      </c>
+      <c r="CA5" s="1">
+        <v>814.0</v>
+      </c>
+      <c r="CB5" s="2">
+        <v>1022.0</v>
+      </c>
+      <c r="CC5" s="2">
+        <v>1551.0</v>
+      </c>
+      <c r="CD5" s="2">
+        <v>1871.0</v>
+      </c>
+      <c r="CE5" s="2">
+        <v>2066.0</v>
+      </c>
+      <c r="CF5" s="2">
+        <v>1479.0</v>
+      </c>
+      <c r="CG5" s="1">
+        <v>600.0</v>
+      </c>
+      <c r="CH5" s="2">
+        <v>19046.0</v>
+      </c>
+      <c r="CI5" s="1">
+        <v>580.0</v>
+      </c>
+      <c r="CJ5" s="2">
+        <v>3388.0</v>
+      </c>
+      <c r="CK5" s="1">
+        <v>671.0</v>
+      </c>
+      <c r="CL5" s="1">
         <v>0.0</v>
       </c>
-      <c r="AK5" s="2">
-        <v>2266.0</v>
-      </c>
-      <c r="AL5" s="2">
-        <v>5032.0</v>
-      </c>
-      <c r="AM5" s="2">
-        <v>15179.0</v>
-      </c>
-      <c r="AN5" s="2">
-        <v>5198.0</v>
-      </c>
-      <c r="AO5" s="2">
-        <v>4378.0</v>
-      </c>
-      <c r="AP5" s="1">
-        <v>105.0</v>
-      </c>
-      <c r="AQ5" s="2">
-        <v>52204.0</v>
-      </c>
-      <c r="AR5" s="2">
-        <v>29163.0</v>
-      </c>
-      <c r="AS5" s="1">
-        <v>107.0</v>
-      </c>
-      <c r="AT5" s="2">
-        <v>1336.0</v>
-      </c>
-      <c r="AU5" s="2">
-        <v>2933.0</v>
-      </c>
-      <c r="AV5" s="2">
-        <v>5292.0</v>
-      </c>
-      <c r="AW5" s="2">
-        <v>2112.0</v>
-      </c>
-      <c r="AX5" s="2">
-        <v>4614.0</v>
-      </c>
-      <c r="AY5" s="2">
-        <v>2722.0</v>
-      </c>
-      <c r="AZ5" s="2">
-        <v>2362.0</v>
-      </c>
-      <c r="BA5" s="2">
-        <v>6785.0</v>
-      </c>
-      <c r="BB5" s="2">
-        <v>1312.0</v>
-      </c>
-      <c r="BC5" s="2">
-        <v>10869.0</v>
-      </c>
-      <c r="BD5" s="2">
-        <v>1907.0</v>
-      </c>
-      <c r="BE5" s="2">
-        <v>5893.0</v>
-      </c>
-      <c r="BF5" s="1">
-        <v>396.0</v>
-      </c>
-      <c r="BG5" s="1">
-        <v>317.0</v>
-      </c>
-      <c r="BH5" s="2">
-        <v>7535.0</v>
-      </c>
-      <c r="BI5" s="2">
-        <v>2049.0</v>
-      </c>
-      <c r="BJ5" s="2">
-        <v>2341.0</v>
-      </c>
-      <c r="BK5" s="2">
-        <v>2911.0</v>
-      </c>
-      <c r="BL5" s="2">
-        <v>5338.0</v>
-      </c>
-      <c r="BM5" s="2">
-        <v>1451.0</v>
-      </c>
-      <c r="BN5" s="2">
-        <v>18116.0</v>
-      </c>
-      <c r="BO5" s="2">
-        <v>11049.0</v>
-      </c>
-      <c r="BP5" s="2">
-        <v>1617.0</v>
-      </c>
-      <c r="BQ5" s="2">
-        <v>2961.0</v>
-      </c>
-      <c r="BR5" s="2">
-        <v>7963.0</v>
-      </c>
-      <c r="BS5" s="2">
-        <v>1119.0</v>
-      </c>
-      <c r="BT5" s="1">
-        <v>172.0</v>
-      </c>
-      <c r="BU5" s="2">
-        <v>2364.0</v>
-      </c>
-      <c r="BV5" s="1">
-        <v>843.0</v>
-      </c>
-      <c r="BW5" s="2">
-        <v>2182.0</v>
-      </c>
-      <c r="BX5" s="2">
-        <v>17117.0</v>
-      </c>
-      <c r="BY5" s="2">
-        <v>2396.0</v>
-      </c>
-      <c r="BZ5" s="2">
-        <v>5318.0</v>
-      </c>
-      <c r="CA5" s="2">
-        <v>1791.0</v>
-      </c>
-      <c r="CB5" s="1">
-        <v>245.0</v>
-      </c>
-      <c r="CC5" s="1">
-        <v>814.0</v>
-      </c>
-      <c r="CD5" s="2">
-        <v>1022.0</v>
-      </c>
-      <c r="CE5" s="2">
-        <v>1551.0</v>
-      </c>
-      <c r="CF5" s="2">
-        <v>1871.0</v>
-      </c>
-      <c r="CG5" s="2">
-        <v>2066.0</v>
-      </c>
-      <c r="CH5" s="2">
-        <v>1479.0</v>
-      </c>
-      <c r="CI5" s="1">
-        <v>600.0</v>
-      </c>
-      <c r="CJ5" s="2">
-        <v>19046.0</v>
-      </c>
-      <c r="CK5" s="1">
-        <v>580.0</v>
-      </c>
-      <c r="CL5" s="2">
-        <v>3388.0</v>
-      </c>
-      <c r="CM5" s="1">
-        <v>671.0</v>
-      </c>
-      <c r="CN5" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="CO5" s="2">
+      <c r="CM5" s="2">
         <v>5590.0</v>
       </c>
-      <c r="CP5" s="2">
+      <c r="CN5" s="2">
         <v>5468.0</v>
       </c>
-      <c r="CQ5" s="1">
+      <c r="CO5" s="1">
         <v>127.0</v>
       </c>
     </row>
@@ -1514,190 +1492,184 @@
       <c r="AG6" s="2">
         <v>9953.0</v>
       </c>
-      <c r="AH6" s="1">
+      <c r="AH6" s="2">
+        <v>1155.0</v>
+      </c>
+      <c r="AI6" s="1">
         <v>0.0</v>
       </c>
-      <c r="AI6" s="2">
-        <v>1155.0</v>
-      </c>
-      <c r="AJ6" s="1">
+      <c r="AJ6" s="2">
+        <v>2379.0</v>
+      </c>
+      <c r="AK6" s="2">
+        <v>6622.0</v>
+      </c>
+      <c r="AL6" s="2">
+        <v>16055.0</v>
+      </c>
+      <c r="AM6" s="2">
+        <v>4829.0</v>
+      </c>
+      <c r="AN6" s="2">
+        <v>3350.0</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="AP6" s="2">
+        <v>61278.0</v>
+      </c>
+      <c r="AQ6" s="2">
+        <v>32857.0</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="AS6" s="2">
+        <v>1389.0</v>
+      </c>
+      <c r="AT6" s="2">
+        <v>1994.0</v>
+      </c>
+      <c r="AU6" s="2">
+        <v>4873.0</v>
+      </c>
+      <c r="AV6" s="2">
+        <v>2837.0</v>
+      </c>
+      <c r="AW6" s="2">
+        <v>4589.0</v>
+      </c>
+      <c r="AX6" s="2">
+        <v>2626.0</v>
+      </c>
+      <c r="AY6" s="2">
+        <v>3092.0</v>
+      </c>
+      <c r="AZ6" s="2">
+        <v>4714.0</v>
+      </c>
+      <c r="BA6" s="2">
+        <v>1318.0</v>
+      </c>
+      <c r="BB6" s="2">
+        <v>10264.0</v>
+      </c>
+      <c r="BC6" s="2">
+        <v>2550.0</v>
+      </c>
+      <c r="BD6" s="2">
+        <v>6011.0</v>
+      </c>
+      <c r="BE6" s="1">
+        <v>530.0</v>
+      </c>
+      <c r="BF6" s="2">
+        <v>8160.0</v>
+      </c>
+      <c r="BG6" s="2">
+        <v>2413.0</v>
+      </c>
+      <c r="BH6" s="2">
+        <v>2445.0</v>
+      </c>
+      <c r="BI6" s="2">
+        <v>2936.0</v>
+      </c>
+      <c r="BJ6" s="2">
+        <v>5828.0</v>
+      </c>
+      <c r="BK6" s="2">
+        <v>2079.0</v>
+      </c>
+      <c r="BL6" s="2">
+        <v>19014.0</v>
+      </c>
+      <c r="BM6" s="2">
+        <v>10653.0</v>
+      </c>
+      <c r="BN6" s="2">
+        <v>2740.0</v>
+      </c>
+      <c r="BO6" s="2">
+        <v>2044.0</v>
+      </c>
+      <c r="BP6" s="2">
+        <v>8488.0</v>
+      </c>
+      <c r="BQ6" s="2">
+        <v>1020.0</v>
+      </c>
+      <c r="BR6" s="1">
+        <v>205.0</v>
+      </c>
+      <c r="BS6" s="2">
+        <v>2432.0</v>
+      </c>
+      <c r="BT6" s="2">
+        <v>1653.0</v>
+      </c>
+      <c r="BU6" s="2">
+        <v>1748.0</v>
+      </c>
+      <c r="BV6" s="2">
+        <v>16612.0</v>
+      </c>
+      <c r="BW6" s="2">
+        <v>2290.0</v>
+      </c>
+      <c r="BX6" s="2">
+        <v>4230.0</v>
+      </c>
+      <c r="BY6" s="2">
+        <v>1684.0</v>
+      </c>
+      <c r="BZ6" s="1">
+        <v>393.0</v>
+      </c>
+      <c r="CA6" s="1">
+        <v>683.0</v>
+      </c>
+      <c r="CB6" s="1">
+        <v>744.0</v>
+      </c>
+      <c r="CC6" s="2">
+        <v>2067.0</v>
+      </c>
+      <c r="CD6" s="2">
+        <v>1684.0</v>
+      </c>
+      <c r="CE6" s="2">
+        <v>1620.0</v>
+      </c>
+      <c r="CF6" s="2">
+        <v>1185.0</v>
+      </c>
+      <c r="CG6" s="1">
+        <v>445.0</v>
+      </c>
+      <c r="CH6" s="2">
+        <v>18692.0</v>
+      </c>
+      <c r="CI6" s="1">
+        <v>518.0</v>
+      </c>
+      <c r="CJ6" s="2">
+        <v>3932.0</v>
+      </c>
+      <c r="CK6" s="1">
+        <v>981.0</v>
+      </c>
+      <c r="CL6" s="1">
         <v>0.0</v>
       </c>
-      <c r="AK6" s="2">
-        <v>2379.0</v>
-      </c>
-      <c r="AL6" s="2">
-        <v>6622.0</v>
-      </c>
-      <c r="AM6" s="2">
-        <v>16055.0</v>
-      </c>
-      <c r="AN6" s="2">
-        <v>4829.0</v>
-      </c>
-      <c r="AO6" s="2">
-        <v>3350.0</v>
-      </c>
-      <c r="AP6" s="1">
-        <v>37.0</v>
-      </c>
-      <c r="AQ6" s="2">
-        <v>61278.0</v>
-      </c>
-      <c r="AR6" s="2">
-        <v>32857.0</v>
-      </c>
-      <c r="AS6" s="1">
-        <v>60.0</v>
-      </c>
-      <c r="AT6" s="2">
-        <v>1389.0</v>
-      </c>
-      <c r="AU6" s="2">
-        <v>1994.0</v>
-      </c>
-      <c r="AV6" s="2">
-        <v>4873.0</v>
-      </c>
-      <c r="AW6" s="2">
-        <v>2837.0</v>
-      </c>
-      <c r="AX6" s="2">
-        <v>4589.0</v>
-      </c>
-      <c r="AY6" s="2">
-        <v>2626.0</v>
-      </c>
-      <c r="AZ6" s="2">
-        <v>3092.0</v>
-      </c>
-      <c r="BA6" s="2">
-        <v>4714.0</v>
-      </c>
-      <c r="BB6" s="2">
-        <v>1318.0</v>
-      </c>
-      <c r="BC6" s="2">
-        <v>10264.0</v>
-      </c>
-      <c r="BD6" s="2">
-        <v>2550.0</v>
-      </c>
-      <c r="BE6" s="2">
-        <v>6011.0</v>
-      </c>
-      <c r="BF6" s="1">
-        <v>530.0</v>
-      </c>
-      <c r="BG6" s="1">
-        <v>396.0</v>
-      </c>
-      <c r="BH6" s="2">
-        <v>8160.0</v>
-      </c>
-      <c r="BI6" s="2">
-        <v>2413.0</v>
-      </c>
-      <c r="BJ6" s="2">
-        <v>2445.0</v>
-      </c>
-      <c r="BK6" s="2">
-        <v>2936.0</v>
-      </c>
-      <c r="BL6" s="2">
-        <v>5828.0</v>
-      </c>
-      <c r="BM6" s="2">
-        <v>2079.0</v>
-      </c>
-      <c r="BN6" s="2">
-        <v>19014.0</v>
-      </c>
-      <c r="BO6" s="2">
-        <v>10653.0</v>
-      </c>
-      <c r="BP6" s="2">
-        <v>2740.0</v>
-      </c>
-      <c r="BQ6" s="2">
-        <v>2044.0</v>
-      </c>
-      <c r="BR6" s="2">
-        <v>8488.0</v>
-      </c>
-      <c r="BS6" s="2">
-        <v>1020.0</v>
-      </c>
-      <c r="BT6" s="1">
-        <v>205.0</v>
-      </c>
-      <c r="BU6" s="2">
-        <v>2432.0</v>
-      </c>
-      <c r="BV6" s="2">
-        <v>1653.0</v>
-      </c>
-      <c r="BW6" s="2">
-        <v>1748.0</v>
-      </c>
-      <c r="BX6" s="2">
-        <v>16612.0</v>
-      </c>
-      <c r="BY6" s="2">
-        <v>2290.0</v>
-      </c>
-      <c r="BZ6" s="2">
-        <v>4230.0</v>
-      </c>
-      <c r="CA6" s="2">
-        <v>1684.0</v>
-      </c>
-      <c r="CB6" s="1">
-        <v>393.0</v>
-      </c>
-      <c r="CC6" s="1">
-        <v>683.0</v>
-      </c>
-      <c r="CD6" s="1">
-        <v>744.0</v>
-      </c>
-      <c r="CE6" s="2">
-        <v>2067.0</v>
-      </c>
-      <c r="CF6" s="2">
-        <v>1684.0</v>
-      </c>
-      <c r="CG6" s="2">
-        <v>1620.0</v>
-      </c>
-      <c r="CH6" s="2">
-        <v>1185.0</v>
-      </c>
-      <c r="CI6" s="1">
-        <v>445.0</v>
-      </c>
-      <c r="CJ6" s="2">
-        <v>18692.0</v>
-      </c>
-      <c r="CK6" s="1">
-        <v>518.0</v>
-      </c>
-      <c r="CL6" s="2">
-        <v>3932.0</v>
-      </c>
-      <c r="CM6" s="1">
-        <v>981.0</v>
-      </c>
-      <c r="CN6" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="CO6" s="2">
+      <c r="CM6" s="2">
         <v>6142.0</v>
       </c>
-      <c r="CP6" s="2">
+      <c r="CN6" s="2">
         <v>3811.0</v>
       </c>
-      <c r="CQ6" s="1">
+      <c r="CO6" s="1">
         <v>259.0</v>
       </c>
     </row>
@@ -1801,190 +1773,184 @@
       <c r="AG7" s="2">
         <v>9407.0</v>
       </c>
-      <c r="AH7" s="1">
+      <c r="AH7" s="2">
+        <v>1337.0</v>
+      </c>
+      <c r="AI7" s="1">
         <v>0.0</v>
       </c>
-      <c r="AI7" s="2">
-        <v>1337.0</v>
-      </c>
-      <c r="AJ7" s="1">
+      <c r="AJ7" s="2">
+        <v>3467.0</v>
+      </c>
+      <c r="AK7" s="2">
+        <v>7406.0</v>
+      </c>
+      <c r="AL7" s="2">
+        <v>23335.0</v>
+      </c>
+      <c r="AM7" s="2">
+        <v>4673.0</v>
+      </c>
+      <c r="AN7" s="2">
+        <v>3883.0</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>125.0</v>
+      </c>
+      <c r="AP7" s="2">
+        <v>64036.0</v>
+      </c>
+      <c r="AQ7" s="2">
+        <v>39053.0</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>202.0</v>
+      </c>
+      <c r="AS7" s="2">
+        <v>1641.0</v>
+      </c>
+      <c r="AT7" s="2">
+        <v>2524.0</v>
+      </c>
+      <c r="AU7" s="2">
+        <v>7223.0</v>
+      </c>
+      <c r="AV7" s="2">
+        <v>3732.0</v>
+      </c>
+      <c r="AW7" s="2">
+        <v>5132.0</v>
+      </c>
+      <c r="AX7" s="2">
+        <v>2864.0</v>
+      </c>
+      <c r="AY7" s="2">
+        <v>2847.0</v>
+      </c>
+      <c r="AZ7" s="2">
+        <v>5468.0</v>
+      </c>
+      <c r="BA7" s="2">
+        <v>1690.0</v>
+      </c>
+      <c r="BB7" s="2">
+        <v>10966.0</v>
+      </c>
+      <c r="BC7" s="2">
+        <v>2973.0</v>
+      </c>
+      <c r="BD7" s="2">
+        <v>5078.0</v>
+      </c>
+      <c r="BE7" s="1">
+        <v>402.0</v>
+      </c>
+      <c r="BF7" s="2">
+        <v>8713.0</v>
+      </c>
+      <c r="BG7" s="2">
+        <v>2989.0</v>
+      </c>
+      <c r="BH7" s="2">
+        <v>2738.0</v>
+      </c>
+      <c r="BI7" s="2">
+        <v>3563.0</v>
+      </c>
+      <c r="BJ7" s="2">
+        <v>6442.0</v>
+      </c>
+      <c r="BK7" s="2">
+        <v>2561.0</v>
+      </c>
+      <c r="BL7" s="2">
+        <v>16239.0</v>
+      </c>
+      <c r="BM7" s="2">
+        <v>8617.0</v>
+      </c>
+      <c r="BN7" s="2">
+        <v>1871.0</v>
+      </c>
+      <c r="BO7" s="2">
+        <v>2198.0</v>
+      </c>
+      <c r="BP7" s="2">
+        <v>9293.0</v>
+      </c>
+      <c r="BQ7" s="2">
+        <v>1532.0</v>
+      </c>
+      <c r="BR7" s="1">
+        <v>329.0</v>
+      </c>
+      <c r="BS7" s="2">
+        <v>2902.0</v>
+      </c>
+      <c r="BT7" s="1">
+        <v>655.0</v>
+      </c>
+      <c r="BU7" s="2">
+        <v>2139.0</v>
+      </c>
+      <c r="BV7" s="2">
+        <v>17485.0</v>
+      </c>
+      <c r="BW7" s="2">
+        <v>2296.0</v>
+      </c>
+      <c r="BX7" s="2">
+        <v>4893.0</v>
+      </c>
+      <c r="BY7" s="2">
+        <v>1985.0</v>
+      </c>
+      <c r="BZ7" s="1">
+        <v>325.0</v>
+      </c>
+      <c r="CA7" s="1">
+        <v>477.0</v>
+      </c>
+      <c r="CB7" s="1">
+        <v>997.0</v>
+      </c>
+      <c r="CC7" s="2">
+        <v>2283.0</v>
+      </c>
+      <c r="CD7" s="2">
+        <v>1668.0</v>
+      </c>
+      <c r="CE7" s="2">
+        <v>1776.0</v>
+      </c>
+      <c r="CF7" s="2">
+        <v>1338.0</v>
+      </c>
+      <c r="CG7" s="1">
+        <v>564.0</v>
+      </c>
+      <c r="CH7" s="2">
+        <v>17682.0</v>
+      </c>
+      <c r="CI7" s="1">
+        <v>301.0</v>
+      </c>
+      <c r="CJ7" s="2">
+        <v>3933.0</v>
+      </c>
+      <c r="CK7" s="1">
+        <v>911.0</v>
+      </c>
+      <c r="CL7" s="1">
         <v>0.0</v>
       </c>
-      <c r="AK7" s="2">
-        <v>3467.0</v>
-      </c>
-      <c r="AL7" s="2">
-        <v>7406.0</v>
-      </c>
-      <c r="AM7" s="2">
-        <v>23335.0</v>
-      </c>
-      <c r="AN7" s="2">
-        <v>4673.0</v>
-      </c>
-      <c r="AO7" s="2">
-        <v>3883.0</v>
-      </c>
-      <c r="AP7" s="1">
-        <v>125.0</v>
-      </c>
-      <c r="AQ7" s="2">
-        <v>64036.0</v>
-      </c>
-      <c r="AR7" s="2">
-        <v>39053.0</v>
-      </c>
-      <c r="AS7" s="1">
-        <v>202.0</v>
-      </c>
-      <c r="AT7" s="2">
-        <v>1641.0</v>
-      </c>
-      <c r="AU7" s="2">
-        <v>2524.0</v>
-      </c>
-      <c r="AV7" s="2">
-        <v>7223.0</v>
-      </c>
-      <c r="AW7" s="2">
-        <v>3732.0</v>
-      </c>
-      <c r="AX7" s="2">
-        <v>5132.0</v>
-      </c>
-      <c r="AY7" s="2">
-        <v>2864.0</v>
-      </c>
-      <c r="AZ7" s="2">
-        <v>2847.0</v>
-      </c>
-      <c r="BA7" s="2">
-        <v>5468.0</v>
-      </c>
-      <c r="BB7" s="2">
-        <v>1690.0</v>
-      </c>
-      <c r="BC7" s="2">
-        <v>10966.0</v>
-      </c>
-      <c r="BD7" s="2">
-        <v>2973.0</v>
-      </c>
-      <c r="BE7" s="2">
-        <v>5078.0</v>
-      </c>
-      <c r="BF7" s="1">
-        <v>402.0</v>
-      </c>
-      <c r="BG7" s="1">
-        <v>427.0</v>
-      </c>
-      <c r="BH7" s="2">
-        <v>8713.0</v>
-      </c>
-      <c r="BI7" s="2">
-        <v>2989.0</v>
-      </c>
-      <c r="BJ7" s="2">
-        <v>2738.0</v>
-      </c>
-      <c r="BK7" s="2">
-        <v>3563.0</v>
-      </c>
-      <c r="BL7" s="2">
-        <v>6442.0</v>
-      </c>
-      <c r="BM7" s="2">
-        <v>2561.0</v>
-      </c>
-      <c r="BN7" s="2">
-        <v>16239.0</v>
-      </c>
-      <c r="BO7" s="2">
-        <v>8617.0</v>
-      </c>
-      <c r="BP7" s="2">
-        <v>1871.0</v>
-      </c>
-      <c r="BQ7" s="2">
-        <v>2198.0</v>
-      </c>
-      <c r="BR7" s="2">
-        <v>9293.0</v>
-      </c>
-      <c r="BS7" s="2">
-        <v>1532.0</v>
-      </c>
-      <c r="BT7" s="1">
-        <v>329.0</v>
-      </c>
-      <c r="BU7" s="2">
-        <v>2902.0</v>
-      </c>
-      <c r="BV7" s="1">
-        <v>655.0</v>
-      </c>
-      <c r="BW7" s="2">
-        <v>2139.0</v>
-      </c>
-      <c r="BX7" s="2">
-        <v>17485.0</v>
-      </c>
-      <c r="BY7" s="2">
-        <v>2296.0</v>
-      </c>
-      <c r="BZ7" s="2">
-        <v>4893.0</v>
-      </c>
-      <c r="CA7" s="2">
-        <v>1985.0</v>
-      </c>
-      <c r="CB7" s="1">
-        <v>325.0</v>
-      </c>
-      <c r="CC7" s="1">
-        <v>477.0</v>
-      </c>
-      <c r="CD7" s="1">
-        <v>997.0</v>
-      </c>
-      <c r="CE7" s="2">
-        <v>2283.0</v>
-      </c>
-      <c r="CF7" s="2">
-        <v>1668.0</v>
-      </c>
-      <c r="CG7" s="2">
-        <v>1776.0</v>
-      </c>
-      <c r="CH7" s="2">
-        <v>1338.0</v>
-      </c>
-      <c r="CI7" s="1">
-        <v>564.0</v>
-      </c>
-      <c r="CJ7" s="2">
-        <v>17682.0</v>
-      </c>
-      <c r="CK7" s="1">
-        <v>301.0</v>
-      </c>
-      <c r="CL7" s="2">
-        <v>3933.0</v>
-      </c>
-      <c r="CM7" s="1">
-        <v>911.0</v>
-      </c>
-      <c r="CN7" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="CO7" s="2">
+      <c r="CM7" s="2">
         <v>5968.0</v>
       </c>
-      <c r="CP7" s="2">
+      <c r="CN7" s="2">
         <v>3756.0</v>
       </c>
-      <c r="CQ7" s="1">
+      <c r="CO7" s="1">
         <v>188.0</v>
       </c>
     </row>
@@ -2088,190 +2054,184 @@
       <c r="AG8" s="2">
         <v>9236.0</v>
       </c>
-      <c r="AH8" s="1">
+      <c r="AH8" s="2">
+        <v>1271.0</v>
+      </c>
+      <c r="AI8" s="1">
         <v>0.0</v>
       </c>
-      <c r="AI8" s="2">
-        <v>1271.0</v>
-      </c>
-      <c r="AJ8" s="1">
+      <c r="AJ8" s="2">
+        <v>3429.0</v>
+      </c>
+      <c r="AK8" s="2">
+        <v>8629.0</v>
+      </c>
+      <c r="AL8" s="2">
+        <v>27654.0</v>
+      </c>
+      <c r="AM8" s="2">
+        <v>5148.0</v>
+      </c>
+      <c r="AN8" s="2">
+        <v>4893.0</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="AP8" s="2">
+        <v>62529.0</v>
+      </c>
+      <c r="AQ8" s="2">
+        <v>57831.0</v>
+      </c>
+      <c r="AR8" s="1">
+        <v>137.0</v>
+      </c>
+      <c r="AS8" s="2">
+        <v>2139.0</v>
+      </c>
+      <c r="AT8" s="2">
+        <v>2284.0</v>
+      </c>
+      <c r="AU8" s="2">
+        <v>9092.0</v>
+      </c>
+      <c r="AV8" s="2">
+        <v>6707.0</v>
+      </c>
+      <c r="AW8" s="2">
+        <v>5126.0</v>
+      </c>
+      <c r="AX8" s="2">
+        <v>3086.0</v>
+      </c>
+      <c r="AY8" s="2">
+        <v>3539.0</v>
+      </c>
+      <c r="AZ8" s="2">
+        <v>5615.0</v>
+      </c>
+      <c r="BA8" s="2">
+        <v>1775.0</v>
+      </c>
+      <c r="BB8" s="2">
+        <v>12211.0</v>
+      </c>
+      <c r="BC8" s="2">
+        <v>3103.0</v>
+      </c>
+      <c r="BD8" s="2">
+        <v>5238.0</v>
+      </c>
+      <c r="BE8" s="1">
+        <v>485.0</v>
+      </c>
+      <c r="BF8" s="2">
+        <v>10770.0</v>
+      </c>
+      <c r="BG8" s="2">
+        <v>3448.0</v>
+      </c>
+      <c r="BH8" s="2">
+        <v>3351.0</v>
+      </c>
+      <c r="BI8" s="2">
+        <v>4535.0</v>
+      </c>
+      <c r="BJ8" s="2">
+        <v>6127.0</v>
+      </c>
+      <c r="BK8" s="2">
+        <v>2626.0</v>
+      </c>
+      <c r="BL8" s="2">
+        <v>19352.0</v>
+      </c>
+      <c r="BM8" s="2">
+        <v>10788.0</v>
+      </c>
+      <c r="BN8" s="2">
+        <v>2434.0</v>
+      </c>
+      <c r="BO8" s="2">
+        <v>1785.0</v>
+      </c>
+      <c r="BP8" s="2">
+        <v>9913.0</v>
+      </c>
+      <c r="BQ8" s="2">
+        <v>1962.0</v>
+      </c>
+      <c r="BR8" s="1">
+        <v>396.0</v>
+      </c>
+      <c r="BS8" s="2">
+        <v>2640.0</v>
+      </c>
+      <c r="BT8" s="1">
+        <v>310.0</v>
+      </c>
+      <c r="BU8" s="2">
+        <v>2402.0</v>
+      </c>
+      <c r="BV8" s="2">
+        <v>18418.0</v>
+      </c>
+      <c r="BW8" s="2">
+        <v>2308.0</v>
+      </c>
+      <c r="BX8" s="2">
+        <v>5522.0</v>
+      </c>
+      <c r="BY8" s="2">
+        <v>1751.0</v>
+      </c>
+      <c r="BZ8" s="1">
+        <v>670.0</v>
+      </c>
+      <c r="CA8" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="CB8" s="2">
+        <v>1172.0</v>
+      </c>
+      <c r="CC8" s="2">
+        <v>2094.0</v>
+      </c>
+      <c r="CD8" s="2">
+        <v>1917.0</v>
+      </c>
+      <c r="CE8" s="2">
+        <v>1846.0</v>
+      </c>
+      <c r="CF8" s="2">
+        <v>1342.0</v>
+      </c>
+      <c r="CG8" s="1">
+        <v>466.0</v>
+      </c>
+      <c r="CH8" s="2">
+        <v>21466.0</v>
+      </c>
+      <c r="CI8" s="1">
+        <v>282.0</v>
+      </c>
+      <c r="CJ8" s="2">
+        <v>4118.0</v>
+      </c>
+      <c r="CK8" s="2">
+        <v>1025.0</v>
+      </c>
+      <c r="CL8" s="1">
         <v>0.0</v>
       </c>
-      <c r="AK8" s="2">
-        <v>3429.0</v>
-      </c>
-      <c r="AL8" s="2">
-        <v>8629.0</v>
-      </c>
-      <c r="AM8" s="2">
-        <v>27654.0</v>
-      </c>
-      <c r="AN8" s="2">
-        <v>5148.0</v>
-      </c>
-      <c r="AO8" s="2">
-        <v>4893.0</v>
-      </c>
-      <c r="AP8" s="1">
-        <v>69.0</v>
-      </c>
-      <c r="AQ8" s="2">
-        <v>62529.0</v>
-      </c>
-      <c r="AR8" s="2">
-        <v>57831.0</v>
-      </c>
-      <c r="AS8" s="1">
-        <v>137.0</v>
-      </c>
-      <c r="AT8" s="2">
-        <v>2139.0</v>
-      </c>
-      <c r="AU8" s="2">
-        <v>2284.0</v>
-      </c>
-      <c r="AV8" s="2">
-        <v>9092.0</v>
-      </c>
-      <c r="AW8" s="2">
-        <v>6707.0</v>
-      </c>
-      <c r="AX8" s="2">
-        <v>5126.0</v>
-      </c>
-      <c r="AY8" s="2">
-        <v>3086.0</v>
-      </c>
-      <c r="AZ8" s="2">
-        <v>3539.0</v>
-      </c>
-      <c r="BA8" s="2">
-        <v>5615.0</v>
-      </c>
-      <c r="BB8" s="2">
-        <v>1775.0</v>
-      </c>
-      <c r="BC8" s="2">
-        <v>12211.0</v>
-      </c>
-      <c r="BD8" s="2">
-        <v>3103.0</v>
-      </c>
-      <c r="BE8" s="2">
-        <v>5238.0</v>
-      </c>
-      <c r="BF8" s="1">
-        <v>485.0</v>
-      </c>
-      <c r="BG8" s="1">
-        <v>477.0</v>
-      </c>
-      <c r="BH8" s="2">
-        <v>10770.0</v>
-      </c>
-      <c r="BI8" s="2">
-        <v>3448.0</v>
-      </c>
-      <c r="BJ8" s="2">
-        <v>3351.0</v>
-      </c>
-      <c r="BK8" s="2">
-        <v>4535.0</v>
-      </c>
-      <c r="BL8" s="2">
-        <v>6127.0</v>
-      </c>
-      <c r="BM8" s="2">
-        <v>2626.0</v>
-      </c>
-      <c r="BN8" s="2">
-        <v>19352.0</v>
-      </c>
-      <c r="BO8" s="2">
-        <v>10788.0</v>
-      </c>
-      <c r="BP8" s="2">
-        <v>2434.0</v>
-      </c>
-      <c r="BQ8" s="2">
-        <v>1785.0</v>
-      </c>
-      <c r="BR8" s="2">
-        <v>9913.0</v>
-      </c>
-      <c r="BS8" s="2">
-        <v>1962.0</v>
-      </c>
-      <c r="BT8" s="1">
-        <v>396.0</v>
-      </c>
-      <c r="BU8" s="2">
-        <v>2640.0</v>
-      </c>
-      <c r="BV8" s="1">
-        <v>310.0</v>
-      </c>
-      <c r="BW8" s="2">
-        <v>2402.0</v>
-      </c>
-      <c r="BX8" s="2">
-        <v>18418.0</v>
-      </c>
-      <c r="BY8" s="2">
-        <v>2308.0</v>
-      </c>
-      <c r="BZ8" s="2">
-        <v>5522.0</v>
-      </c>
-      <c r="CA8" s="2">
-        <v>1751.0</v>
-      </c>
-      <c r="CB8" s="1">
-        <v>670.0</v>
-      </c>
-      <c r="CC8" s="1">
-        <v>500.0</v>
-      </c>
-      <c r="CD8" s="2">
-        <v>1172.0</v>
-      </c>
-      <c r="CE8" s="2">
-        <v>2094.0</v>
-      </c>
-      <c r="CF8" s="2">
-        <v>1917.0</v>
-      </c>
-      <c r="CG8" s="2">
-        <v>1846.0</v>
-      </c>
-      <c r="CH8" s="2">
-        <v>1342.0</v>
-      </c>
-      <c r="CI8" s="1">
-        <v>466.0</v>
-      </c>
-      <c r="CJ8" s="2">
-        <v>21466.0</v>
-      </c>
-      <c r="CK8" s="1">
-        <v>282.0</v>
-      </c>
-      <c r="CL8" s="2">
-        <v>4118.0</v>
-      </c>
       <c r="CM8" s="2">
-        <v>1025.0</v>
-      </c>
-      <c r="CN8" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="CO8" s="2">
         <v>6039.0</v>
       </c>
-      <c r="CP8" s="2">
+      <c r="CN8" s="2">
         <v>3394.0</v>
       </c>
-      <c r="CQ8" s="1">
+      <c r="CO8" s="1">
         <v>191.0</v>
       </c>
     </row>
@@ -2375,190 +2335,184 @@
       <c r="AG9" s="2">
         <v>10752.0</v>
       </c>
-      <c r="AH9" s="1">
+      <c r="AH9" s="2">
+        <v>1557.0</v>
+      </c>
+      <c r="AI9" s="1">
         <v>0.0</v>
       </c>
-      <c r="AI9" s="2">
-        <v>1557.0</v>
-      </c>
-      <c r="AJ9" s="1">
-        <v>0.0</v>
+      <c r="AJ9" s="2">
+        <v>3999.0</v>
       </c>
       <c r="AK9" s="2">
-        <v>3999.0</v>
+        <v>11331.0</v>
       </c>
       <c r="AL9" s="2">
-        <v>11331.0</v>
+        <v>33190.0</v>
       </c>
       <c r="AM9" s="2">
-        <v>33190.0</v>
+        <v>5328.0</v>
       </c>
       <c r="AN9" s="2">
-        <v>5328.0</v>
-      </c>
-      <c r="AO9" s="2">
         <v>5761.0</v>
       </c>
-      <c r="AP9" s="1">
+      <c r="AO9" s="1">
         <v>155.0</v>
       </c>
+      <c r="AP9" s="2">
+        <v>62504.0</v>
+      </c>
       <c r="AQ9" s="2">
-        <v>62504.0</v>
-      </c>
-      <c r="AR9" s="2">
         <v>49217.0</v>
       </c>
-      <c r="AS9" s="1">
+      <c r="AR9" s="1">
         <v>116.0</v>
       </c>
+      <c r="AS9" s="2">
+        <v>2253.0</v>
+      </c>
       <c r="AT9" s="2">
-        <v>2253.0</v>
+        <v>2894.0</v>
       </c>
       <c r="AU9" s="2">
-        <v>2894.0</v>
+        <v>9933.0</v>
       </c>
       <c r="AV9" s="2">
-        <v>9933.0</v>
+        <v>9543.0</v>
       </c>
       <c r="AW9" s="2">
-        <v>9543.0</v>
+        <v>5495.0</v>
       </c>
       <c r="AX9" s="2">
-        <v>5495.0</v>
+        <v>3333.0</v>
       </c>
       <c r="AY9" s="2">
-        <v>3333.0</v>
+        <v>3836.0</v>
       </c>
       <c r="AZ9" s="2">
-        <v>3836.0</v>
+        <v>8821.0</v>
       </c>
       <c r="BA9" s="2">
-        <v>8821.0</v>
+        <v>1454.0</v>
       </c>
       <c r="BB9" s="2">
-        <v>1454.0</v>
+        <v>13066.0</v>
       </c>
       <c r="BC9" s="2">
-        <v>13066.0</v>
+        <v>3806.0</v>
       </c>
       <c r="BD9" s="2">
-        <v>3806.0</v>
-      </c>
-      <c r="BE9" s="2">
         <v>8527.0</v>
       </c>
-      <c r="BF9" s="1">
+      <c r="BE9" s="1">
         <v>458.0</v>
       </c>
-      <c r="BG9" s="1">
-        <v>515.0</v>
+      <c r="BF9" s="2">
+        <v>13479.0</v>
+      </c>
+      <c r="BG9" s="2">
+        <v>3741.0</v>
       </c>
       <c r="BH9" s="2">
-        <v>13479.0</v>
+        <v>3545.0</v>
       </c>
       <c r="BI9" s="2">
-        <v>3741.0</v>
+        <v>5244.0</v>
       </c>
       <c r="BJ9" s="2">
-        <v>3545.0</v>
+        <v>6841.0</v>
       </c>
       <c r="BK9" s="2">
-        <v>5244.0</v>
+        <v>2173.0</v>
       </c>
       <c r="BL9" s="2">
-        <v>6841.0</v>
+        <v>18548.0</v>
       </c>
       <c r="BM9" s="2">
-        <v>2173.0</v>
+        <v>8712.0</v>
       </c>
       <c r="BN9" s="2">
-        <v>18548.0</v>
+        <v>3028.0</v>
       </c>
       <c r="BO9" s="2">
-        <v>8712.0</v>
+        <v>3531.0</v>
       </c>
       <c r="BP9" s="2">
-        <v>3028.0</v>
+        <v>12133.0</v>
       </c>
       <c r="BQ9" s="2">
-        <v>3531.0</v>
-      </c>
-      <c r="BR9" s="2">
-        <v>12133.0</v>
+        <v>1805.0</v>
+      </c>
+      <c r="BR9" s="1">
+        <v>355.0</v>
       </c>
       <c r="BS9" s="2">
-        <v>1805.0</v>
+        <v>2852.0</v>
       </c>
       <c r="BT9" s="1">
-        <v>355.0</v>
+        <v>611.0</v>
       </c>
       <c r="BU9" s="2">
-        <v>2852.0</v>
-      </c>
-      <c r="BV9" s="1">
-        <v>611.0</v>
+        <v>2955.0</v>
+      </c>
+      <c r="BV9" s="2">
+        <v>19395.0</v>
       </c>
       <c r="BW9" s="2">
-        <v>2955.0</v>
+        <v>2377.0</v>
       </c>
       <c r="BX9" s="2">
-        <v>19395.0</v>
+        <v>5873.0</v>
       </c>
       <c r="BY9" s="2">
-        <v>2377.0</v>
-      </c>
-      <c r="BZ9" s="2">
-        <v>5873.0</v>
-      </c>
-      <c r="CA9" s="2">
         <v>1750.0</v>
       </c>
-      <c r="CB9" s="1">
+      <c r="BZ9" s="1">
         <v>540.0</v>
       </c>
-      <c r="CC9" s="1">
+      <c r="CA9" s="1">
         <v>484.0</v>
       </c>
+      <c r="CB9" s="2">
+        <v>1119.0</v>
+      </c>
+      <c r="CC9" s="2">
+        <v>2854.0</v>
+      </c>
       <c r="CD9" s="2">
-        <v>1119.0</v>
+        <v>2131.0</v>
       </c>
       <c r="CE9" s="2">
-        <v>2854.0</v>
+        <v>2214.0</v>
       </c>
       <c r="CF9" s="2">
-        <v>2131.0</v>
-      </c>
-      <c r="CG9" s="2">
-        <v>2214.0</v>
+        <v>1250.0</v>
+      </c>
+      <c r="CG9" s="1">
+        <v>521.0</v>
       </c>
       <c r="CH9" s="2">
-        <v>1250.0</v>
+        <v>16674.0</v>
       </c>
       <c r="CI9" s="1">
-        <v>521.0</v>
+        <v>302.0</v>
       </c>
       <c r="CJ9" s="2">
-        <v>16674.0</v>
-      </c>
-      <c r="CK9" s="1">
-        <v>302.0</v>
-      </c>
-      <c r="CL9" s="2">
         <v>4080.0</v>
       </c>
+      <c r="CK9" s="2">
+        <v>1317.0</v>
+      </c>
+      <c r="CL9" s="1">
+        <v>453.0</v>
+      </c>
       <c r="CM9" s="2">
-        <v>1317.0</v>
-      </c>
-      <c r="CN9" s="1">
-        <v>453.0</v>
-      </c>
-      <c r="CO9" s="2">
         <v>8035.0</v>
       </c>
-      <c r="CP9" s="2">
+      <c r="CN9" s="2">
         <v>3834.0</v>
       </c>
-      <c r="CQ9" s="1">
+      <c r="CO9" s="1">
         <v>231.0</v>
       </c>
     </row>
@@ -2662,190 +2616,184 @@
       <c r="AG10" s="2">
         <v>8692.0</v>
       </c>
-      <c r="AH10" s="1">
+      <c r="AH10" s="2">
+        <v>1951.0</v>
+      </c>
+      <c r="AI10" s="1">
         <v>0.0</v>
       </c>
-      <c r="AI10" s="2">
-        <v>1951.0</v>
-      </c>
-      <c r="AJ10" s="1">
-        <v>0.0</v>
+      <c r="AJ10" s="2">
+        <v>4524.0</v>
       </c>
       <c r="AK10" s="2">
-        <v>4524.0</v>
+        <v>13116.0</v>
       </c>
       <c r="AL10" s="2">
-        <v>13116.0</v>
+        <v>34227.0</v>
       </c>
       <c r="AM10" s="2">
-        <v>34227.0</v>
+        <v>7326.0</v>
       </c>
       <c r="AN10" s="2">
-        <v>7326.0</v>
-      </c>
-      <c r="AO10" s="2">
         <v>6283.0</v>
       </c>
-      <c r="AP10" s="1">
+      <c r="AO10" s="1">
         <v>194.0</v>
       </c>
+      <c r="AP10" s="2">
+        <v>64509.0</v>
+      </c>
       <c r="AQ10" s="2">
-        <v>64509.0</v>
-      </c>
-      <c r="AR10" s="2">
         <v>71347.0</v>
       </c>
-      <c r="AS10" s="1">
+      <c r="AR10" s="1">
         <v>173.0</v>
       </c>
+      <c r="AS10" s="2">
+        <v>2472.0</v>
+      </c>
       <c r="AT10" s="2">
-        <v>2472.0</v>
+        <v>3562.0</v>
       </c>
       <c r="AU10" s="2">
-        <v>3562.0</v>
+        <v>15584.0</v>
       </c>
       <c r="AV10" s="2">
-        <v>15584.0</v>
+        <v>12299.0</v>
       </c>
       <c r="AW10" s="2">
-        <v>12299.0</v>
+        <v>6449.0</v>
       </c>
       <c r="AX10" s="2">
-        <v>6449.0</v>
+        <v>3700.0</v>
       </c>
       <c r="AY10" s="2">
-        <v>3700.0</v>
+        <v>4894.0</v>
       </c>
       <c r="AZ10" s="2">
-        <v>4894.0</v>
+        <v>9993.0</v>
       </c>
       <c r="BA10" s="2">
-        <v>9993.0</v>
+        <v>1666.0</v>
       </c>
       <c r="BB10" s="2">
-        <v>1666.0</v>
+        <v>16034.0</v>
       </c>
       <c r="BC10" s="2">
-        <v>16034.0</v>
+        <v>4695.0</v>
       </c>
       <c r="BD10" s="2">
-        <v>4695.0</v>
-      </c>
-      <c r="BE10" s="2">
         <v>9981.0</v>
       </c>
-      <c r="BF10" s="1">
+      <c r="BE10" s="1">
         <v>576.0</v>
       </c>
-      <c r="BG10" s="1">
-        <v>609.0</v>
+      <c r="BF10" s="2">
+        <v>16092.0</v>
+      </c>
+      <c r="BG10" s="2">
+        <v>3983.0</v>
       </c>
       <c r="BH10" s="2">
-        <v>16092.0</v>
+        <v>4221.0</v>
       </c>
       <c r="BI10" s="2">
-        <v>3983.0</v>
+        <v>5749.0</v>
       </c>
       <c r="BJ10" s="2">
-        <v>4221.0</v>
+        <v>7315.0</v>
       </c>
       <c r="BK10" s="2">
-        <v>5749.0</v>
+        <v>2980.0</v>
       </c>
       <c r="BL10" s="2">
-        <v>7315.0</v>
+        <v>23985.0</v>
       </c>
       <c r="BM10" s="2">
-        <v>2980.0</v>
+        <v>11189.0</v>
       </c>
       <c r="BN10" s="2">
-        <v>23985.0</v>
+        <v>4313.0</v>
       </c>
       <c r="BO10" s="2">
-        <v>11189.0</v>
+        <v>4025.0</v>
       </c>
       <c r="BP10" s="2">
-        <v>4313.0</v>
+        <v>15265.0</v>
       </c>
       <c r="BQ10" s="2">
-        <v>4025.0</v>
-      </c>
-      <c r="BR10" s="2">
-        <v>15265.0</v>
+        <v>2505.0</v>
+      </c>
+      <c r="BR10" s="1">
+        <v>149.0</v>
       </c>
       <c r="BS10" s="2">
-        <v>2505.0</v>
+        <v>3463.0</v>
       </c>
       <c r="BT10" s="1">
-        <v>149.0</v>
+        <v>282.0</v>
       </c>
       <c r="BU10" s="2">
-        <v>3463.0</v>
-      </c>
-      <c r="BV10" s="1">
-        <v>282.0</v>
+        <v>3005.0</v>
+      </c>
+      <c r="BV10" s="2">
+        <v>21278.0</v>
       </c>
       <c r="BW10" s="2">
-        <v>3005.0</v>
+        <v>2932.0</v>
       </c>
       <c r="BX10" s="2">
-        <v>21278.0</v>
+        <v>5707.0</v>
       </c>
       <c r="BY10" s="2">
-        <v>2932.0</v>
-      </c>
-      <c r="BZ10" s="2">
-        <v>5707.0</v>
-      </c>
-      <c r="CA10" s="2">
         <v>1526.0</v>
       </c>
-      <c r="CB10" s="1">
+      <c r="BZ10" s="1">
         <v>679.0</v>
       </c>
-      <c r="CC10" s="1">
+      <c r="CA10" s="1">
         <v>692.0</v>
       </c>
+      <c r="CB10" s="2">
+        <v>1444.0</v>
+      </c>
+      <c r="CC10" s="2">
+        <v>2701.0</v>
+      </c>
       <c r="CD10" s="2">
-        <v>1444.0</v>
+        <v>2635.0</v>
       </c>
       <c r="CE10" s="2">
-        <v>2701.0</v>
+        <v>2740.0</v>
       </c>
       <c r="CF10" s="2">
-        <v>2635.0</v>
-      </c>
-      <c r="CG10" s="2">
-        <v>2740.0</v>
+        <v>1874.0</v>
+      </c>
+      <c r="CG10" s="1">
+        <v>624.0</v>
       </c>
       <c r="CH10" s="2">
-        <v>1874.0</v>
+        <v>17980.0</v>
       </c>
       <c r="CI10" s="1">
-        <v>624.0</v>
+        <v>359.0</v>
       </c>
       <c r="CJ10" s="2">
-        <v>17980.0</v>
-      </c>
-      <c r="CK10" s="1">
-        <v>359.0</v>
-      </c>
-      <c r="CL10" s="2">
         <v>4730.0</v>
       </c>
+      <c r="CK10" s="2">
+        <v>1429.0</v>
+      </c>
+      <c r="CL10" s="1">
+        <v>608.0</v>
+      </c>
       <c r="CM10" s="2">
-        <v>1429.0</v>
-      </c>
-      <c r="CN10" s="1">
-        <v>608.0</v>
-      </c>
-      <c r="CO10" s="2">
         <v>8616.0</v>
       </c>
-      <c r="CP10" s="2">
+      <c r="CN10" s="2">
         <v>3668.0</v>
       </c>
-      <c r="CQ10" s="1">
+      <c r="CO10" s="1">
         <v>309.0</v>
       </c>
     </row>
@@ -2949,190 +2897,184 @@
       <c r="AG11" s="2">
         <v>15766.0</v>
       </c>
-      <c r="AH11" s="1">
+      <c r="AH11" s="2">
+        <v>2477.0</v>
+      </c>
+      <c r="AI11" s="1">
         <v>0.0</v>
       </c>
-      <c r="AI11" s="2">
-        <v>2477.0</v>
-      </c>
-      <c r="AJ11" s="1">
-        <v>0.0</v>
+      <c r="AJ11" s="2">
+        <v>5216.0</v>
       </c>
       <c r="AK11" s="2">
-        <v>5216.0</v>
+        <v>16529.0</v>
       </c>
       <c r="AL11" s="2">
-        <v>16529.0</v>
+        <v>38051.0</v>
       </c>
       <c r="AM11" s="2">
-        <v>38051.0</v>
+        <v>9105.0</v>
       </c>
       <c r="AN11" s="2">
-        <v>9105.0</v>
-      </c>
-      <c r="AO11" s="2">
         <v>6902.0</v>
       </c>
-      <c r="AP11" s="1">
+      <c r="AO11" s="1">
         <v>322.0</v>
       </c>
+      <c r="AP11" s="2">
+        <v>66112.0</v>
+      </c>
       <c r="AQ11" s="2">
-        <v>66112.0</v>
-      </c>
-      <c r="AR11" s="2">
         <v>81219.0</v>
       </c>
-      <c r="AS11" s="1">
+      <c r="AR11" s="1">
         <v>115.0</v>
       </c>
+      <c r="AS11" s="2">
+        <v>3501.0</v>
+      </c>
       <c r="AT11" s="2">
-        <v>3501.0</v>
+        <v>3595.0</v>
       </c>
       <c r="AU11" s="2">
-        <v>3595.0</v>
+        <v>16674.0</v>
       </c>
       <c r="AV11" s="2">
-        <v>16674.0</v>
+        <v>14451.0</v>
       </c>
       <c r="AW11" s="2">
-        <v>14451.0</v>
+        <v>7729.0</v>
       </c>
       <c r="AX11" s="2">
-        <v>7729.0</v>
+        <v>4472.0</v>
       </c>
       <c r="AY11" s="2">
-        <v>4472.0</v>
+        <v>6451.0</v>
       </c>
       <c r="AZ11" s="2">
-        <v>6451.0</v>
+        <v>11602.0</v>
       </c>
       <c r="BA11" s="2">
-        <v>11602.0</v>
+        <v>1654.0</v>
       </c>
       <c r="BB11" s="2">
-        <v>1654.0</v>
+        <v>18797.0</v>
       </c>
       <c r="BC11" s="2">
-        <v>18797.0</v>
+        <v>6080.0</v>
       </c>
       <c r="BD11" s="2">
-        <v>6080.0</v>
+        <v>11807.0</v>
       </c>
       <c r="BE11" s="2">
-        <v>11807.0</v>
+        <v>1150.0</v>
       </c>
       <c r="BF11" s="2">
-        <v>1150.0</v>
-      </c>
-      <c r="BG11" s="1">
-        <v>722.0</v>
+        <v>20376.0</v>
+      </c>
+      <c r="BG11" s="2">
+        <v>3998.0</v>
       </c>
       <c r="BH11" s="2">
-        <v>20376.0</v>
+        <v>4434.0</v>
       </c>
       <c r="BI11" s="2">
-        <v>3998.0</v>
+        <v>6330.0</v>
       </c>
       <c r="BJ11" s="2">
-        <v>4434.0</v>
+        <v>9368.0</v>
       </c>
       <c r="BK11" s="2">
-        <v>6330.0</v>
+        <v>3490.0</v>
       </c>
       <c r="BL11" s="2">
-        <v>9368.0</v>
+        <v>29065.0</v>
       </c>
       <c r="BM11" s="2">
-        <v>3490.0</v>
+        <v>12878.0</v>
       </c>
       <c r="BN11" s="2">
-        <v>29065.0</v>
+        <v>3854.0</v>
       </c>
       <c r="BO11" s="2">
-        <v>12878.0</v>
+        <v>4770.0</v>
       </c>
       <c r="BP11" s="2">
-        <v>3854.0</v>
+        <v>20788.0</v>
       </c>
       <c r="BQ11" s="2">
-        <v>4770.0</v>
-      </c>
-      <c r="BR11" s="2">
-        <v>20788.0</v>
+        <v>3203.0</v>
+      </c>
+      <c r="BR11" s="1">
+        <v>147.0</v>
       </c>
       <c r="BS11" s="2">
-        <v>3203.0</v>
+        <v>5470.0</v>
       </c>
       <c r="BT11" s="1">
-        <v>147.0</v>
+        <v>733.0</v>
       </c>
       <c r="BU11" s="2">
-        <v>5470.0</v>
-      </c>
-      <c r="BV11" s="1">
-        <v>733.0</v>
+        <v>3454.0</v>
+      </c>
+      <c r="BV11" s="2">
+        <v>22827.0</v>
       </c>
       <c r="BW11" s="2">
-        <v>3454.0</v>
+        <v>3443.0</v>
       </c>
       <c r="BX11" s="2">
-        <v>22827.0</v>
+        <v>6470.0</v>
       </c>
       <c r="BY11" s="2">
-        <v>3443.0</v>
-      </c>
-      <c r="BZ11" s="2">
-        <v>6470.0</v>
-      </c>
-      <c r="CA11" s="2">
         <v>1666.0</v>
       </c>
-      <c r="CB11" s="1">
+      <c r="BZ11" s="1">
         <v>819.0</v>
       </c>
-      <c r="CC11" s="1">
+      <c r="CA11" s="1">
         <v>743.0</v>
       </c>
+      <c r="CB11" s="2">
+        <v>1634.0</v>
+      </c>
+      <c r="CC11" s="2">
+        <v>2841.0</v>
+      </c>
       <c r="CD11" s="2">
-        <v>1634.0</v>
+        <v>3332.0</v>
       </c>
       <c r="CE11" s="2">
-        <v>2841.0</v>
+        <v>3274.0</v>
       </c>
       <c r="CF11" s="2">
-        <v>3332.0</v>
-      </c>
-      <c r="CG11" s="2">
-        <v>3274.0</v>
+        <v>1747.0</v>
+      </c>
+      <c r="CG11" s="1">
+        <v>690.0</v>
       </c>
       <c r="CH11" s="2">
-        <v>1747.0</v>
+        <v>22656.0</v>
       </c>
       <c r="CI11" s="1">
-        <v>690.0</v>
+        <v>505.0</v>
       </c>
       <c r="CJ11" s="2">
-        <v>22656.0</v>
-      </c>
-      <c r="CK11" s="1">
-        <v>505.0</v>
-      </c>
-      <c r="CL11" s="2">
         <v>5397.0</v>
       </c>
+      <c r="CK11" s="2">
+        <v>1552.0</v>
+      </c>
+      <c r="CL11" s="1">
+        <v>383.0</v>
+      </c>
       <c r="CM11" s="2">
-        <v>1552.0</v>
-      </c>
-      <c r="CN11" s="1">
-        <v>383.0</v>
-      </c>
-      <c r="CO11" s="2">
         <v>10215.0</v>
       </c>
-      <c r="CP11" s="2">
+      <c r="CN11" s="2">
         <v>4888.0</v>
       </c>
-      <c r="CQ11" s="1">
+      <c r="CO11" s="1">
         <v>382.0</v>
       </c>
     </row>
@@ -3236,190 +3178,184 @@
       <c r="AG12" s="2">
         <v>16563.0</v>
       </c>
-      <c r="AH12" s="1">
+      <c r="AH12" s="2">
+        <v>3777.0</v>
+      </c>
+      <c r="AI12" s="1">
         <v>0.0</v>
       </c>
-      <c r="AI12" s="2">
-        <v>3777.0</v>
-      </c>
-      <c r="AJ12" s="1">
-        <v>0.0</v>
+      <c r="AJ12" s="2">
+        <v>5667.0</v>
       </c>
       <c r="AK12" s="2">
-        <v>5667.0</v>
+        <v>16199.0</v>
       </c>
       <c r="AL12" s="2">
-        <v>16199.0</v>
+        <v>48050.0</v>
       </c>
       <c r="AM12" s="2">
-        <v>48050.0</v>
+        <v>10896.0</v>
       </c>
       <c r="AN12" s="2">
-        <v>10896.0</v>
-      </c>
-      <c r="AO12" s="2">
         <v>6701.0</v>
       </c>
-      <c r="AP12" s="1">
+      <c r="AO12" s="1">
         <v>259.0</v>
       </c>
+      <c r="AP12" s="2">
+        <v>46543.0</v>
+      </c>
       <c r="AQ12" s="2">
-        <v>46543.0</v>
-      </c>
-      <c r="AR12" s="2">
         <v>83026.0</v>
       </c>
-      <c r="AS12" s="1">
+      <c r="AR12" s="1">
         <v>56.0</v>
       </c>
+      <c r="AS12" s="2">
+        <v>4134.0</v>
+      </c>
       <c r="AT12" s="2">
-        <v>4134.0</v>
+        <v>4033.0</v>
       </c>
       <c r="AU12" s="2">
-        <v>4033.0</v>
+        <v>18351.0</v>
       </c>
       <c r="AV12" s="2">
-        <v>18351.0</v>
+        <v>13985.0</v>
       </c>
       <c r="AW12" s="2">
-        <v>13985.0</v>
+        <v>7926.0</v>
       </c>
       <c r="AX12" s="2">
-        <v>7926.0</v>
+        <v>4400.0</v>
       </c>
       <c r="AY12" s="2">
-        <v>4400.0</v>
+        <v>6902.0</v>
       </c>
       <c r="AZ12" s="2">
-        <v>6902.0</v>
+        <v>10585.0</v>
       </c>
       <c r="BA12" s="2">
-        <v>10585.0</v>
+        <v>2002.0</v>
       </c>
       <c r="BB12" s="2">
-        <v>2002.0</v>
+        <v>20402.0</v>
       </c>
       <c r="BC12" s="2">
-        <v>20402.0</v>
+        <v>6780.0</v>
       </c>
       <c r="BD12" s="2">
-        <v>6780.0</v>
+        <v>12880.0</v>
       </c>
       <c r="BE12" s="2">
-        <v>12880.0</v>
+        <v>2011.0</v>
       </c>
       <c r="BF12" s="2">
-        <v>2011.0</v>
-      </c>
-      <c r="BG12" s="1">
-        <v>768.0</v>
+        <v>20290.0</v>
+      </c>
+      <c r="BG12" s="2">
+        <v>4359.0</v>
       </c>
       <c r="BH12" s="2">
-        <v>20290.0</v>
+        <v>5193.0</v>
       </c>
       <c r="BI12" s="2">
-        <v>4359.0</v>
+        <v>7429.0</v>
       </c>
       <c r="BJ12" s="2">
-        <v>5193.0</v>
+        <v>11333.0</v>
       </c>
       <c r="BK12" s="2">
-        <v>7429.0</v>
+        <v>4693.0</v>
       </c>
       <c r="BL12" s="2">
-        <v>11333.0</v>
+        <v>31822.0</v>
       </c>
       <c r="BM12" s="2">
-        <v>4693.0</v>
+        <v>13193.0</v>
       </c>
       <c r="BN12" s="2">
-        <v>31822.0</v>
+        <v>3801.0</v>
       </c>
       <c r="BO12" s="2">
-        <v>13193.0</v>
+        <v>5473.0</v>
       </c>
       <c r="BP12" s="2">
-        <v>3801.0</v>
+        <v>24321.0</v>
       </c>
       <c r="BQ12" s="2">
-        <v>5473.0</v>
-      </c>
-      <c r="BR12" s="2">
-        <v>24321.0</v>
+        <v>3657.0</v>
+      </c>
+      <c r="BR12" s="1">
+        <v>28.0</v>
       </c>
       <c r="BS12" s="2">
-        <v>3657.0</v>
+        <v>5478.0</v>
       </c>
       <c r="BT12" s="1">
-        <v>28.0</v>
+        <v>777.0</v>
       </c>
       <c r="BU12" s="2">
-        <v>5478.0</v>
-      </c>
-      <c r="BV12" s="1">
-        <v>777.0</v>
+        <v>4242.0</v>
+      </c>
+      <c r="BV12" s="2">
+        <v>27935.0</v>
       </c>
       <c r="BW12" s="2">
-        <v>4242.0</v>
+        <v>4076.0</v>
       </c>
       <c r="BX12" s="2">
-        <v>27935.0</v>
+        <v>7689.0</v>
       </c>
       <c r="BY12" s="2">
-        <v>4076.0</v>
-      </c>
-      <c r="BZ12" s="2">
-        <v>7689.0</v>
-      </c>
-      <c r="CA12" s="2">
         <v>2009.0</v>
       </c>
-      <c r="CB12" s="1">
+      <c r="BZ12" s="1">
         <v>807.0</v>
       </c>
-      <c r="CC12" s="1">
+      <c r="CA12" s="1">
         <v>672.0</v>
       </c>
+      <c r="CB12" s="2">
+        <v>2122.0</v>
+      </c>
+      <c r="CC12" s="2">
+        <v>2846.0</v>
+      </c>
       <c r="CD12" s="2">
-        <v>2122.0</v>
+        <v>3546.0</v>
       </c>
       <c r="CE12" s="2">
-        <v>2846.0</v>
+        <v>3814.0</v>
       </c>
       <c r="CF12" s="2">
-        <v>3546.0</v>
-      </c>
-      <c r="CG12" s="2">
-        <v>3814.0</v>
+        <v>2157.0</v>
+      </c>
+      <c r="CG12" s="1">
+        <v>599.0</v>
       </c>
       <c r="CH12" s="2">
-        <v>2157.0</v>
+        <v>26626.0</v>
       </c>
       <c r="CI12" s="1">
-        <v>599.0</v>
+        <v>658.0</v>
       </c>
       <c r="CJ12" s="2">
-        <v>26626.0</v>
-      </c>
-      <c r="CK12" s="1">
-        <v>658.0</v>
-      </c>
-      <c r="CL12" s="2">
         <v>5689.0</v>
       </c>
+      <c r="CK12" s="2">
+        <v>2058.0</v>
+      </c>
+      <c r="CL12" s="1">
+        <v>442.0</v>
+      </c>
       <c r="CM12" s="2">
-        <v>2058.0</v>
-      </c>
-      <c r="CN12" s="1">
-        <v>442.0</v>
-      </c>
-      <c r="CO12" s="2">
         <v>10026.0</v>
       </c>
-      <c r="CP12" s="2">
+      <c r="CN12" s="2">
         <v>4196.0</v>
       </c>
-      <c r="CQ12" s="1">
+      <c r="CO12" s="1">
         <v>648.0</v>
       </c>
     </row>
@@ -3523,190 +3459,184 @@
       <c r="AG13" s="2">
         <v>11529.0</v>
       </c>
-      <c r="AH13" s="1">
-        <v>0.0</v>
+      <c r="AH13" s="2">
+        <v>3951.0</v>
       </c>
       <c r="AI13" s="2">
-        <v>3951.0</v>
+        <v>25010.0</v>
       </c>
       <c r="AJ13" s="2">
-        <v>25010.0</v>
+        <v>6556.0</v>
       </c>
       <c r="AK13" s="2">
-        <v>6556.0</v>
+        <v>11977.0</v>
       </c>
       <c r="AL13" s="2">
-        <v>11977.0</v>
+        <v>38990.0</v>
       </c>
       <c r="AM13" s="2">
-        <v>38990.0</v>
+        <v>12144.0</v>
       </c>
       <c r="AN13" s="2">
-        <v>12144.0</v>
-      </c>
-      <c r="AO13" s="2">
         <v>5572.0</v>
       </c>
-      <c r="AP13" s="1">
+      <c r="AO13" s="1">
         <v>271.0</v>
       </c>
+      <c r="AP13" s="2">
+        <v>33091.0</v>
+      </c>
       <c r="AQ13" s="2">
-        <v>33091.0</v>
-      </c>
-      <c r="AR13" s="2">
         <v>93041.0</v>
       </c>
-      <c r="AS13" s="1">
+      <c r="AR13" s="1">
         <v>290.0</v>
       </c>
+      <c r="AS13" s="2">
+        <v>3860.0</v>
+      </c>
       <c r="AT13" s="2">
-        <v>3860.0</v>
+        <v>3705.0</v>
       </c>
       <c r="AU13" s="2">
-        <v>3705.0</v>
+        <v>16851.0</v>
       </c>
       <c r="AV13" s="2">
-        <v>16851.0</v>
+        <v>7584.0</v>
       </c>
       <c r="AW13" s="2">
-        <v>7584.0</v>
+        <v>8169.0</v>
       </c>
       <c r="AX13" s="2">
-        <v>8169.0</v>
+        <v>4141.0</v>
       </c>
       <c r="AY13" s="2">
-        <v>4141.0</v>
+        <v>7101.0</v>
       </c>
       <c r="AZ13" s="2">
-        <v>7101.0</v>
+        <v>8702.0</v>
       </c>
       <c r="BA13" s="2">
-        <v>8702.0</v>
+        <v>2620.0</v>
       </c>
       <c r="BB13" s="2">
-        <v>2620.0</v>
+        <v>18113.0</v>
       </c>
       <c r="BC13" s="2">
-        <v>18113.0</v>
+        <v>7348.0</v>
       </c>
       <c r="BD13" s="2">
-        <v>7348.0</v>
+        <v>14682.0</v>
       </c>
       <c r="BE13" s="2">
-        <v>14682.0</v>
+        <v>1780.0</v>
       </c>
       <c r="BF13" s="2">
-        <v>1780.0</v>
+        <v>17482.0</v>
       </c>
       <c r="BG13" s="2">
-        <v>701857.0</v>
+        <v>4577.0</v>
       </c>
       <c r="BH13" s="2">
-        <v>17482.0</v>
+        <v>4666.0</v>
       </c>
       <c r="BI13" s="2">
-        <v>4577.0</v>
+        <v>5932.0</v>
       </c>
       <c r="BJ13" s="2">
-        <v>4666.0</v>
+        <v>10415.0</v>
       </c>
       <c r="BK13" s="2">
-        <v>5932.0</v>
+        <v>4195.0</v>
       </c>
       <c r="BL13" s="2">
-        <v>10415.0</v>
+        <v>27784.0</v>
       </c>
       <c r="BM13" s="2">
-        <v>4195.0</v>
+        <v>11429.0</v>
       </c>
       <c r="BN13" s="2">
-        <v>27784.0</v>
+        <v>2178.0</v>
       </c>
       <c r="BO13" s="2">
-        <v>11429.0</v>
+        <v>4634.0</v>
       </c>
       <c r="BP13" s="2">
-        <v>2178.0</v>
+        <v>15144.0</v>
       </c>
       <c r="BQ13" s="2">
-        <v>4634.0</v>
-      </c>
-      <c r="BR13" s="2">
-        <v>15144.0</v>
+        <v>3821.0</v>
+      </c>
+      <c r="BR13" s="1">
+        <v>91.0</v>
       </c>
       <c r="BS13" s="2">
-        <v>3821.0</v>
-      </c>
-      <c r="BT13" s="1">
-        <v>91.0</v>
+        <v>5344.0</v>
+      </c>
+      <c r="BT13" s="2">
+        <v>1313.0</v>
       </c>
       <c r="BU13" s="2">
-        <v>5344.0</v>
+        <v>5525.0</v>
       </c>
       <c r="BV13" s="2">
-        <v>1313.0</v>
+        <v>24347.0</v>
       </c>
       <c r="BW13" s="2">
-        <v>5525.0</v>
+        <v>3463.0</v>
       </c>
       <c r="BX13" s="2">
-        <v>24347.0</v>
+        <v>9089.0</v>
       </c>
       <c r="BY13" s="2">
-        <v>3463.0</v>
-      </c>
-      <c r="BZ13" s="2">
-        <v>9089.0</v>
-      </c>
-      <c r="CA13" s="2">
         <v>1710.0</v>
       </c>
-      <c r="CB13" s="1">
+      <c r="BZ13" s="1">
         <v>867.0</v>
       </c>
-      <c r="CC13" s="1">
+      <c r="CA13" s="1">
         <v>814.0</v>
       </c>
+      <c r="CB13" s="2">
+        <v>2267.0</v>
+      </c>
+      <c r="CC13" s="2">
+        <v>1857.0</v>
+      </c>
       <c r="CD13" s="2">
-        <v>2267.0</v>
+        <v>3413.0</v>
       </c>
       <c r="CE13" s="2">
-        <v>1857.0</v>
+        <v>3964.0</v>
       </c>
       <c r="CF13" s="2">
-        <v>3413.0</v>
-      </c>
-      <c r="CG13" s="2">
-        <v>3964.0</v>
+        <v>2214.0</v>
+      </c>
+      <c r="CG13" s="1">
+        <v>658.0</v>
       </c>
       <c r="CH13" s="2">
-        <v>2214.0</v>
+        <v>24004.0</v>
       </c>
       <c r="CI13" s="1">
-        <v>658.0</v>
+        <v>750.0</v>
       </c>
       <c r="CJ13" s="2">
-        <v>24004.0</v>
-      </c>
-      <c r="CK13" s="1">
-        <v>750.0</v>
-      </c>
-      <c r="CL13" s="2">
         <v>5617.0</v>
       </c>
+      <c r="CK13" s="2">
+        <v>1907.0</v>
+      </c>
+      <c r="CL13" s="1">
+        <v>583.0</v>
+      </c>
       <c r="CM13" s="2">
-        <v>1907.0</v>
-      </c>
-      <c r="CN13" s="1">
-        <v>583.0</v>
-      </c>
-      <c r="CO13" s="2">
         <v>9230.0</v>
       </c>
-      <c r="CP13" s="2">
+      <c r="CN13" s="2">
         <v>4613.0</v>
       </c>
-      <c r="CQ13" s="1">
+      <c r="CO13" s="1">
         <v>752.0</v>
       </c>
     </row>
@@ -3780,8 +3710,8 @@
       <c r="W14" s="2">
         <v>81683.0</v>
       </c>
-      <c r="X14" s="1">
-        <v>0.0</v>
+      <c r="X14" s="2">
+        <v>70812.0</v>
       </c>
       <c r="Y14" s="2">
         <v>14713.0</v>
@@ -3811,189 +3741,183 @@
         <v>13612.0</v>
       </c>
       <c r="AH14" s="2">
-        <v>70812.0</v>
+        <v>2046.0</v>
       </c>
       <c r="AI14" s="2">
-        <v>2046.0</v>
+        <v>30679.0</v>
       </c>
       <c r="AJ14" s="2">
-        <v>30679.0</v>
+        <v>5466.0</v>
       </c>
       <c r="AK14" s="2">
-        <v>5466.0</v>
+        <v>14572.0</v>
       </c>
       <c r="AL14" s="2">
-        <v>14572.0</v>
+        <v>42761.0</v>
       </c>
       <c r="AM14" s="2">
-        <v>42761.0</v>
+        <v>12122.0</v>
       </c>
       <c r="AN14" s="2">
-        <v>12122.0</v>
-      </c>
-      <c r="AO14" s="2">
         <v>5217.0</v>
       </c>
-      <c r="AP14" s="1">
+      <c r="AO14" s="1">
         <v>262.0</v>
       </c>
+      <c r="AP14" s="2">
+        <v>22825.0</v>
+      </c>
       <c r="AQ14" s="2">
-        <v>22825.0</v>
-      </c>
-      <c r="AR14" s="2">
         <v>89283.0</v>
       </c>
-      <c r="AS14" s="1">
+      <c r="AR14" s="1">
         <v>397.0</v>
       </c>
+      <c r="AS14" s="2">
+        <v>3706.0</v>
+      </c>
       <c r="AT14" s="2">
-        <v>3706.0</v>
+        <v>6647.0</v>
       </c>
       <c r="AU14" s="2">
-        <v>6647.0</v>
+        <v>19217.0</v>
       </c>
       <c r="AV14" s="2">
-        <v>19217.0</v>
+        <v>9598.0</v>
       </c>
       <c r="AW14" s="2">
-        <v>9598.0</v>
+        <v>6210.0</v>
       </c>
       <c r="AX14" s="2">
-        <v>6210.0</v>
+        <v>3458.0</v>
       </c>
       <c r="AY14" s="2">
-        <v>3458.0</v>
+        <v>7331.0</v>
       </c>
       <c r="AZ14" s="2">
-        <v>7331.0</v>
+        <v>10231.0</v>
       </c>
       <c r="BA14" s="2">
-        <v>10231.0</v>
+        <v>2146.0</v>
       </c>
       <c r="BB14" s="2">
-        <v>2146.0</v>
+        <v>18508.0</v>
       </c>
       <c r="BC14" s="2">
-        <v>18508.0</v>
+        <v>6211.0</v>
       </c>
       <c r="BD14" s="2">
-        <v>6211.0</v>
+        <v>12665.0</v>
       </c>
       <c r="BE14" s="2">
-        <v>12665.0</v>
+        <v>2563.0</v>
       </c>
       <c r="BF14" s="2">
-        <v>2563.0</v>
+        <v>21264.0</v>
       </c>
       <c r="BG14" s="2">
-        <v>716930.0</v>
+        <v>4206.0</v>
       </c>
       <c r="BH14" s="2">
-        <v>21264.0</v>
+        <v>5321.0</v>
       </c>
       <c r="BI14" s="2">
-        <v>4206.0</v>
+        <v>6238.0</v>
       </c>
       <c r="BJ14" s="2">
-        <v>5321.0</v>
+        <v>13839.0</v>
       </c>
       <c r="BK14" s="2">
-        <v>6238.0</v>
+        <v>4807.0</v>
       </c>
       <c r="BL14" s="2">
-        <v>13839.0</v>
+        <v>26611.0</v>
       </c>
       <c r="BM14" s="2">
-        <v>4807.0</v>
+        <v>8557.0</v>
       </c>
       <c r="BN14" s="2">
-        <v>26611.0</v>
+        <v>2337.0</v>
       </c>
       <c r="BO14" s="2">
-        <v>8557.0</v>
+        <v>4326.0</v>
       </c>
       <c r="BP14" s="2">
-        <v>2337.0</v>
+        <v>12385.0</v>
       </c>
       <c r="BQ14" s="2">
-        <v>4326.0</v>
-      </c>
-      <c r="BR14" s="2">
-        <v>12385.0</v>
+        <v>4224.0</v>
+      </c>
+      <c r="BR14" s="1">
+        <v>8.0</v>
       </c>
       <c r="BS14" s="2">
-        <v>4224.0</v>
-      </c>
-      <c r="BT14" s="1">
-        <v>8.0</v>
+        <v>4266.0</v>
+      </c>
+      <c r="BT14" s="2">
+        <v>1608.0</v>
       </c>
       <c r="BU14" s="2">
-        <v>4266.0</v>
+        <v>4602.0</v>
       </c>
       <c r="BV14" s="2">
-        <v>1608.0</v>
+        <v>23045.0</v>
       </c>
       <c r="BW14" s="2">
-        <v>4602.0</v>
+        <v>3922.0</v>
       </c>
       <c r="BX14" s="2">
-        <v>23045.0</v>
+        <v>9095.0</v>
       </c>
       <c r="BY14" s="2">
-        <v>3922.0</v>
+        <v>2489.0</v>
       </c>
       <c r="BZ14" s="2">
-        <v>9095.0</v>
+        <v>1065.0</v>
       </c>
       <c r="CA14" s="2">
-        <v>2489.0</v>
+        <v>1216.0</v>
       </c>
       <c r="CB14" s="2">
-        <v>1065.0</v>
+        <v>2129.0</v>
       </c>
       <c r="CC14" s="2">
-        <v>1216.0</v>
+        <v>1332.0</v>
       </c>
       <c r="CD14" s="2">
-        <v>2129.0</v>
+        <v>3184.0</v>
       </c>
       <c r="CE14" s="2">
-        <v>1332.0</v>
+        <v>3913.0</v>
       </c>
       <c r="CF14" s="2">
-        <v>3184.0</v>
-      </c>
-      <c r="CG14" s="2">
-        <v>3913.0</v>
+        <v>2450.0</v>
+      </c>
+      <c r="CG14" s="1">
+        <v>470.0</v>
       </c>
       <c r="CH14" s="2">
-        <v>2450.0</v>
+        <v>25444.0</v>
       </c>
       <c r="CI14" s="1">
-        <v>470.0</v>
+        <v>757.0</v>
       </c>
       <c r="CJ14" s="2">
-        <v>25444.0</v>
-      </c>
-      <c r="CK14" s="1">
-        <v>757.0</v>
-      </c>
-      <c r="CL14" s="2">
         <v>6154.0</v>
       </c>
+      <c r="CK14" s="2">
+        <v>1744.0</v>
+      </c>
+      <c r="CL14" s="1">
+        <v>969.0</v>
+      </c>
       <c r="CM14" s="2">
-        <v>1744.0</v>
-      </c>
-      <c r="CN14" s="1">
-        <v>969.0</v>
-      </c>
-      <c r="CO14" s="2">
         <v>8952.0</v>
       </c>
-      <c r="CP14" s="2">
+      <c r="CN14" s="2">
         <v>4842.0</v>
       </c>
-      <c r="CQ14" s="1">
+      <c r="CO14" s="1">
         <v>812.0</v>
       </c>
     </row>
@@ -4067,8 +3991,8 @@
       <c r="W15" s="2">
         <v>89430.0</v>
       </c>
-      <c r="X15" s="1">
-        <v>0.0</v>
+      <c r="X15" s="2">
+        <v>73217.0</v>
       </c>
       <c r="Y15" s="2">
         <v>14986.0</v>
@@ -4098,189 +4022,183 @@
         <v>17115.0</v>
       </c>
       <c r="AH15" s="2">
-        <v>73217.0</v>
+        <v>2407.0</v>
       </c>
       <c r="AI15" s="2">
-        <v>2407.0</v>
+        <v>32796.0</v>
       </c>
       <c r="AJ15" s="2">
-        <v>32796.0</v>
+        <v>6280.0</v>
       </c>
       <c r="AK15" s="2">
-        <v>6280.0</v>
+        <v>15108.0</v>
       </c>
       <c r="AL15" s="2">
-        <v>15108.0</v>
+        <v>45058.0</v>
       </c>
       <c r="AM15" s="2">
-        <v>45058.0</v>
+        <v>14813.0</v>
       </c>
       <c r="AN15" s="2">
-        <v>14813.0</v>
-      </c>
-      <c r="AO15" s="2">
         <v>5854.0</v>
       </c>
-      <c r="AP15" s="1">
+      <c r="AO15" s="1">
         <v>258.0</v>
       </c>
+      <c r="AP15" s="2">
+        <v>23587.0</v>
+      </c>
       <c r="AQ15" s="2">
-        <v>23587.0</v>
-      </c>
-      <c r="AR15" s="2">
         <v>97348.0</v>
       </c>
-      <c r="AS15" s="1">
+      <c r="AR15" s="1">
         <v>263.0</v>
       </c>
+      <c r="AS15" s="2">
+        <v>3720.0</v>
+      </c>
       <c r="AT15" s="2">
-        <v>3720.0</v>
+        <v>7778.0</v>
       </c>
       <c r="AU15" s="2">
-        <v>7778.0</v>
+        <v>24015.0</v>
       </c>
       <c r="AV15" s="2">
-        <v>24015.0</v>
+        <v>10706.0</v>
       </c>
       <c r="AW15" s="2">
-        <v>10706.0</v>
+        <v>7774.0</v>
       </c>
       <c r="AX15" s="2">
-        <v>7774.0</v>
+        <v>4673.0</v>
       </c>
       <c r="AY15" s="2">
-        <v>4673.0</v>
+        <v>9220.0</v>
       </c>
       <c r="AZ15" s="2">
-        <v>9220.0</v>
+        <v>10077.0</v>
       </c>
       <c r="BA15" s="2">
-        <v>10077.0</v>
+        <v>2649.0</v>
       </c>
       <c r="BB15" s="2">
-        <v>2649.0</v>
+        <v>20636.0</v>
       </c>
       <c r="BC15" s="2">
-        <v>20636.0</v>
+        <v>6462.0</v>
       </c>
       <c r="BD15" s="2">
-        <v>6462.0</v>
+        <v>13293.0</v>
       </c>
       <c r="BE15" s="2">
-        <v>13293.0</v>
+        <v>3235.0</v>
       </c>
       <c r="BF15" s="2">
-        <v>3235.0</v>
+        <v>22584.0</v>
       </c>
       <c r="BG15" s="2">
-        <v>785561.0</v>
+        <v>4346.0</v>
       </c>
       <c r="BH15" s="2">
-        <v>22584.0</v>
+        <v>5859.0</v>
       </c>
       <c r="BI15" s="2">
-        <v>4346.0</v>
+        <v>7471.0</v>
       </c>
       <c r="BJ15" s="2">
-        <v>5859.0</v>
+        <v>16285.0</v>
       </c>
       <c r="BK15" s="2">
-        <v>7471.0</v>
+        <v>2357.0</v>
       </c>
       <c r="BL15" s="2">
-        <v>16285.0</v>
+        <v>31620.0</v>
       </c>
       <c r="BM15" s="2">
-        <v>2357.0</v>
+        <v>11854.0</v>
       </c>
       <c r="BN15" s="2">
-        <v>31620.0</v>
+        <v>2900.0</v>
       </c>
       <c r="BO15" s="2">
-        <v>11854.0</v>
+        <v>5822.0</v>
       </c>
       <c r="BP15" s="2">
-        <v>2900.0</v>
+        <v>17671.0</v>
       </c>
       <c r="BQ15" s="2">
-        <v>5822.0</v>
-      </c>
-      <c r="BR15" s="2">
-        <v>17671.0</v>
+        <v>4294.0</v>
+      </c>
+      <c r="BR15" s="1">
+        <v>44.0</v>
       </c>
       <c r="BS15" s="2">
-        <v>4294.0</v>
-      </c>
-      <c r="BT15" s="1">
-        <v>44.0</v>
+        <v>6955.0</v>
+      </c>
+      <c r="BT15" s="2">
+        <v>1398.0</v>
       </c>
       <c r="BU15" s="2">
-        <v>6955.0</v>
+        <v>5625.0</v>
       </c>
       <c r="BV15" s="2">
-        <v>1398.0</v>
+        <v>23684.0</v>
       </c>
       <c r="BW15" s="2">
-        <v>5625.0</v>
+        <v>4718.0</v>
       </c>
       <c r="BX15" s="2">
-        <v>23684.0</v>
+        <v>10413.0</v>
       </c>
       <c r="BY15" s="2">
-        <v>4718.0</v>
+        <v>1872.0</v>
       </c>
       <c r="BZ15" s="2">
-        <v>10413.0</v>
+        <v>1197.0</v>
       </c>
       <c r="CA15" s="2">
-        <v>1872.0</v>
+        <v>1247.0</v>
       </c>
       <c r="CB15" s="2">
-        <v>1197.0</v>
+        <v>2502.0</v>
       </c>
       <c r="CC15" s="2">
-        <v>1247.0</v>
+        <v>2038.0</v>
       </c>
       <c r="CD15" s="2">
-        <v>2502.0</v>
+        <v>3692.0</v>
       </c>
       <c r="CE15" s="2">
-        <v>2038.0</v>
+        <v>5039.0</v>
       </c>
       <c r="CF15" s="2">
-        <v>3692.0</v>
-      </c>
-      <c r="CG15" s="2">
-        <v>5039.0</v>
+        <v>2104.0</v>
+      </c>
+      <c r="CG15" s="1">
+        <v>505.0</v>
       </c>
       <c r="CH15" s="2">
-        <v>2104.0</v>
+        <v>30479.0</v>
       </c>
       <c r="CI15" s="1">
-        <v>505.0</v>
+        <v>744.0</v>
       </c>
       <c r="CJ15" s="2">
-        <v>30479.0</v>
-      </c>
-      <c r="CK15" s="1">
-        <v>744.0</v>
-      </c>
-      <c r="CL15" s="2">
         <v>6845.0</v>
       </c>
+      <c r="CK15" s="2">
+        <v>1937.0</v>
+      </c>
+      <c r="CL15" s="1">
+        <v>937.0</v>
+      </c>
       <c r="CM15" s="2">
-        <v>1937.0</v>
-      </c>
-      <c r="CN15" s="1">
-        <v>937.0</v>
-      </c>
-      <c r="CO15" s="2">
         <v>8599.0</v>
       </c>
-      <c r="CP15" s="2">
+      <c r="CN15" s="2">
         <v>4659.0</v>
       </c>
-      <c r="CQ15" s="1">
+      <c r="CO15" s="1">
         <v>799.0</v>
       </c>
     </row>
@@ -4354,8 +4272,8 @@
       <c r="W16" s="2">
         <v>87285.0</v>
       </c>
-      <c r="X16" s="1">
-        <v>0.0</v>
+      <c r="X16" s="2">
+        <v>87651.0</v>
       </c>
       <c r="Y16" s="2">
         <v>15059.0</v>
@@ -4385,189 +4303,183 @@
         <v>19968.0</v>
       </c>
       <c r="AH16" s="2">
-        <v>87651.0</v>
+        <v>3251.0</v>
       </c>
       <c r="AI16" s="2">
-        <v>3251.0</v>
+        <v>35306.0</v>
       </c>
       <c r="AJ16" s="2">
-        <v>35306.0</v>
+        <v>6359.0</v>
       </c>
       <c r="AK16" s="2">
-        <v>6359.0</v>
+        <v>16095.0</v>
       </c>
       <c r="AL16" s="2">
-        <v>16095.0</v>
+        <v>41758.0</v>
       </c>
       <c r="AM16" s="2">
-        <v>41758.0</v>
+        <v>14824.0</v>
       </c>
       <c r="AN16" s="2">
-        <v>14824.0</v>
-      </c>
-      <c r="AO16" s="2">
         <v>5377.0</v>
       </c>
-      <c r="AP16" s="1">
+      <c r="AO16" s="1">
         <v>384.0</v>
       </c>
+      <c r="AP16" s="2">
+        <v>42551.0</v>
+      </c>
       <c r="AQ16" s="2">
-        <v>42551.0</v>
-      </c>
-      <c r="AR16" s="2">
         <v>81075.0</v>
       </c>
-      <c r="AS16" s="1">
+      <c r="AR16" s="1">
         <v>436.0</v>
       </c>
+      <c r="AS16" s="2">
+        <v>4358.0</v>
+      </c>
       <c r="AT16" s="2">
-        <v>4358.0</v>
+        <v>7808.0</v>
       </c>
       <c r="AU16" s="2">
-        <v>7808.0</v>
+        <v>25083.0</v>
       </c>
       <c r="AV16" s="2">
-        <v>25083.0</v>
+        <v>10168.0</v>
       </c>
       <c r="AW16" s="2">
-        <v>10168.0</v>
+        <v>7814.0</v>
       </c>
       <c r="AX16" s="2">
-        <v>7814.0</v>
+        <v>4633.0</v>
       </c>
       <c r="AY16" s="2">
-        <v>4633.0</v>
+        <v>10314.0</v>
       </c>
       <c r="AZ16" s="2">
-        <v>10314.0</v>
+        <v>11704.0</v>
       </c>
       <c r="BA16" s="2">
-        <v>11704.0</v>
+        <v>3116.0</v>
       </c>
       <c r="BB16" s="2">
-        <v>3116.0</v>
+        <v>22634.0</v>
       </c>
       <c r="BC16" s="2">
-        <v>22634.0</v>
+        <v>7400.0</v>
       </c>
       <c r="BD16" s="2">
-        <v>7400.0</v>
+        <v>11386.0</v>
       </c>
       <c r="BE16" s="2">
-        <v>11386.0</v>
+        <v>2692.0</v>
       </c>
       <c r="BF16" s="2">
-        <v>2692.0</v>
+        <v>24177.0</v>
       </c>
       <c r="BG16" s="2">
-        <v>838029.0</v>
+        <v>2985.0</v>
       </c>
       <c r="BH16" s="2">
-        <v>24177.0</v>
+        <v>5204.0</v>
       </c>
       <c r="BI16" s="2">
-        <v>2985.0</v>
+        <v>7809.0</v>
       </c>
       <c r="BJ16" s="2">
-        <v>5204.0</v>
+        <v>16740.0</v>
       </c>
       <c r="BK16" s="2">
-        <v>7809.0</v>
+        <v>2907.0</v>
       </c>
       <c r="BL16" s="2">
-        <v>16740.0</v>
+        <v>39013.0</v>
       </c>
       <c r="BM16" s="2">
-        <v>2907.0</v>
+        <v>15675.0</v>
       </c>
       <c r="BN16" s="2">
-        <v>39013.0</v>
+        <v>3583.0</v>
       </c>
       <c r="BO16" s="2">
-        <v>15675.0</v>
+        <v>6427.0</v>
       </c>
       <c r="BP16" s="2">
-        <v>3583.0</v>
+        <v>24276.0</v>
       </c>
       <c r="BQ16" s="2">
-        <v>6427.0</v>
-      </c>
-      <c r="BR16" s="2">
-        <v>24276.0</v>
+        <v>4508.0</v>
+      </c>
+      <c r="BR16" s="1">
+        <v>26.0</v>
       </c>
       <c r="BS16" s="2">
-        <v>4508.0</v>
-      </c>
-      <c r="BT16" s="1">
-        <v>26.0</v>
+        <v>7171.0</v>
+      </c>
+      <c r="BT16" s="2">
+        <v>1298.0</v>
       </c>
       <c r="BU16" s="2">
-        <v>7171.0</v>
+        <v>4756.0</v>
       </c>
       <c r="BV16" s="2">
-        <v>1298.0</v>
+        <v>27085.0</v>
       </c>
       <c r="BW16" s="2">
-        <v>4756.0</v>
+        <v>5429.0</v>
       </c>
       <c r="BX16" s="2">
-        <v>27085.0</v>
+        <v>10684.0</v>
       </c>
       <c r="BY16" s="2">
-        <v>5429.0</v>
+        <v>2010.0</v>
       </c>
       <c r="BZ16" s="2">
-        <v>10684.0</v>
-      </c>
-      <c r="CA16" s="2">
-        <v>2010.0</v>
+        <v>1266.0</v>
+      </c>
+      <c r="CA16" s="1">
+        <v>993.0</v>
       </c>
       <c r="CB16" s="2">
-        <v>1266.0</v>
-      </c>
-      <c r="CC16" s="1">
-        <v>993.0</v>
+        <v>2773.0</v>
+      </c>
+      <c r="CC16" s="2">
+        <v>1392.0</v>
       </c>
       <c r="CD16" s="2">
-        <v>2773.0</v>
+        <v>4290.0</v>
       </c>
       <c r="CE16" s="2">
-        <v>1392.0</v>
+        <v>3949.0</v>
       </c>
       <c r="CF16" s="2">
-        <v>4290.0</v>
-      </c>
-      <c r="CG16" s="2">
-        <v>3949.0</v>
+        <v>1537.0</v>
+      </c>
+      <c r="CG16" s="1">
+        <v>645.0</v>
       </c>
       <c r="CH16" s="2">
-        <v>1537.0</v>
+        <v>29538.0</v>
       </c>
       <c r="CI16" s="1">
-        <v>645.0</v>
+        <v>702.0</v>
       </c>
       <c r="CJ16" s="2">
-        <v>29538.0</v>
-      </c>
-      <c r="CK16" s="1">
-        <v>702.0</v>
+        <v>7338.0</v>
+      </c>
+      <c r="CK16" s="2">
+        <v>2154.0</v>
       </c>
       <c r="CL16" s="2">
-        <v>7338.0</v>
+        <v>2973.0</v>
       </c>
       <c r="CM16" s="2">
-        <v>2154.0</v>
+        <v>9068.0</v>
       </c>
       <c r="CN16" s="2">
-        <v>2973.0</v>
-      </c>
-      <c r="CO16" s="2">
-        <v>9068.0</v>
-      </c>
-      <c r="CP16" s="2">
         <v>5520.0</v>
       </c>
-      <c r="CQ16" s="1">
+      <c r="CO16" s="1">
         <v>891.0</v>
       </c>
     </row>
